--- a/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
@@ -26,10 +26,648 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
+  <si>
+    <t>  1. CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>  1. REFERENCE INFORMATION</t>
+  </si>
+  <si>
+    <t>  2. ACTIVE LOG TABLE</t>
+  </si>
+  <si>
+    <t>  3. PERIODIC REVIEW / CLOSURE</t>
+  </si>
+  <si>
+    <t>  4. PERIODIC REVIEW SIGN-OFF</t>
+  </si>
+  <si>
+    <t>  EXPIRY CONTROL WINDOWS</t>
+  </si>
+  <si>
+    <t>  REFERENCE / SOURCE CONTEXT</t>
+  </si>
+  <si>
+    <t>  SUPPORT TABLE</t>
+  </si>
+  <si>
+    <t>=ROW()-ROW($A$14)+1</t>
+  </si>
+  <si>
+    <t>ABSENT</t>
+  </si>
+  <si>
+    <t>ACCEPT</t>
+  </si>
+  <si>
+    <t>ACCEPT WITH ACTION</t>
+  </si>
+  <si>
+    <t>APPROVED</t>
+  </si>
+  <si>
+    <t>ATTENDANCE_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZATION_STATUS</t>
+  </si>
+  <si>
+    <t>AUTHORIZED</t>
+  </si>
+  <si>
+    <t>AWARE</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Approved By</t>
+  </si>
+  <si>
+    <t>Boundary / SoR</t>
+  </si>
+  <si>
+    <t>CERTIFICATION BODY</t>
+  </si>
+  <si>
+    <t>CERTIFICATION TRACKING LOG</t>
+  </si>
+  <si>
+    <t>CERTIFICATION TRACKING LOG — CONTROLLED LOOKUP LISTS</t>
+  </si>
+  <si>
+    <t>CERTIFICATION TRACKING LOG — EVIDENCE REFERENCE REGISTER</t>
+  </si>
+  <si>
+    <t>CERTIFICATION TRACKING LOG — EXPIRY QUEUE / FOLLOW-UP</t>
+  </si>
+  <si>
+    <t>CERT_STATUS</t>
+  </si>
+  <si>
+    <t>CLASSROOM</t>
+  </si>
+  <si>
+    <t>CLIMATE_SCENARIO</t>
+  </si>
+  <si>
+    <t>CLOSED</t>
+  </si>
+  <si>
+    <t>COACHING</t>
+  </si>
+  <si>
+    <t>COMBINED</t>
+  </si>
+  <si>
+    <t>COMMUNITY</t>
+  </si>
+  <si>
+    <t>COMPETENCY_LEVEL</t>
+  </si>
+  <si>
+    <t>COMPLIANCE</t>
+  </si>
+  <si>
+    <t>CONDITIONAL</t>
+  </si>
+  <si>
+    <t>CONTEXT_CLASS</t>
+  </si>
+  <si>
+    <t>CONTRACTUAL</t>
+  </si>
+  <si>
+    <t>COPY_ACTION</t>
+  </si>
+  <si>
+    <t>CRITICAL</t>
+  </si>
+  <si>
+    <t>CSR_CLASS</t>
+  </si>
+  <si>
+    <t>CURRENCY</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>Cert Status</t>
+  </si>
+  <si>
+    <t>Certification Log ID</t>
+  </si>
+  <si>
+    <t>Certification tracking log monitors renewals / expiry and status; references certificates rather than reassessing competence itself.</t>
+  </si>
+  <si>
+    <t>Comments</t>
+  </si>
+  <si>
+    <t>Competency Level</t>
+  </si>
+  <si>
+    <t>DECISION</t>
+  </si>
+  <si>
+    <t>DELIVERY</t>
+  </si>
+  <si>
+    <t>DEPT</t>
+  </si>
+  <si>
+    <t>DESTROY</t>
+  </si>
+  <si>
+    <t>DEVELOPMENT_PRIORITY</t>
+  </si>
+  <si>
+    <t>DOC_STATUS</t>
+  </si>
+  <si>
+    <t>DRAFT</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Department / Scope</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>EFFECTIVE</t>
+  </si>
+  <si>
+    <t>EMPLOYEE</t>
+  </si>
+  <si>
+    <t>ENG</t>
+  </si>
+  <si>
+    <t>ENVIRONMENT</t>
+  </si>
+  <si>
+    <t>ENVIRONMENTAL</t>
+  </si>
+  <si>
+    <t>ESG</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>EXCUSED</t>
+  </si>
+  <si>
+    <t>EXPIRED</t>
+  </si>
+  <si>
+    <t>EXPIRING</t>
+  </si>
+  <si>
+    <t>EXTERNAL COURSE</t>
+  </si>
+  <si>
+    <t>Eff. Date</t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Evidence Folder Ref</t>
+  </si>
+  <si>
+    <t>Evidence ID</t>
+  </si>
+  <si>
+    <t>Evidence Ref</t>
+  </si>
+  <si>
+    <t>Excel Table — certification tracker (freeze / filter required)</t>
+  </si>
+  <si>
+    <t>Expiring Items</t>
+  </si>
+  <si>
+    <t>Expiry Date</t>
+  </si>
+  <si>
+    <t>FACILITY</t>
+  </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>FINANCE</t>
+  </si>
+  <si>
+    <t>FRM-806</t>
+  </si>
+  <si>
+    <t>Final Status</t>
+  </si>
+  <si>
+    <t>Form Code</t>
+  </si>
+  <si>
+    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
+  </si>
+  <si>
+    <t>HIGH</t>
+  </si>
+  <si>
+    <t>HOLD</t>
+  </si>
+  <si>
+    <t>HR</t>
+  </si>
+  <si>
+    <t>HR + Department Manager</t>
+  </si>
+  <si>
+    <t>HSE</t>
+  </si>
+  <si>
+    <t>IN PROGRESS</t>
+  </si>
+  <si>
+    <t>INCIDENT_CLASS</t>
+  </si>
+  <si>
+    <t>INDEPENDENT</t>
+  </si>
+  <si>
+    <t>INSPECTION</t>
+  </si>
+  <si>
+    <t>INSURANCE</t>
+  </si>
+  <si>
+    <t>INTERNAL</t>
+  </si>
+  <si>
+    <t>ISSUE</t>
+  </si>
+  <si>
+    <t>ISSUE_ACTION</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Issue Date</t>
+  </si>
+  <si>
+    <t>JPY</t>
+  </si>
+  <si>
+    <t>LATE</t>
+  </si>
+  <si>
+    <t>LEGAL</t>
+  </si>
+  <si>
+    <t>LIGHTING_AREA</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>M365 evidence / shared workbook</t>
+  </si>
+  <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
+    <t>MEETING ROOM</t>
+  </si>
+  <si>
+    <t>MGT</t>
+  </si>
+  <si>
+    <t>MONITORING</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NOT AUTHORIZED</t>
+  </si>
+  <si>
+    <t>NOT TRAINED</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
+  </si>
+  <si>
+    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
+  </si>
+  <si>
+    <t>NOTICE: Keep one row per certification or requalification item. Record issue date, expiry date, current status, owner and the next action before the item becomes overdue.</t>
+  </si>
+  <si>
+    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
+  </si>
+  <si>
+    <t>Name / Signature / Date</t>
+  </si>
+  <si>
+    <t>Next Action</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>OBSERVATION</t>
+  </si>
+  <si>
+    <t>OBSOLETE</t>
+  </si>
+  <si>
+    <t>OFFICE</t>
+  </si>
+  <si>
+    <t>OJT</t>
+  </si>
+  <si>
+    <t>ON HOLD</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>OTHER</t>
+  </si>
+  <si>
+    <t>OUTDOOR</t>
+  </si>
+  <si>
+    <t>OWNER</t>
+  </si>
+  <si>
+    <t>Owner</t>
+  </si>
+  <si>
+    <t>PACKAGING</t>
+  </si>
+  <si>
+    <t>PARTY_TYPE</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PESTLE</t>
+  </si>
+  <si>
+    <t>PHYSICAL ACUTE</t>
+  </si>
+  <si>
+    <t>PHYSICAL CHRONIC</t>
+  </si>
+  <si>
+    <t>PLANNED</t>
+  </si>
+  <si>
+    <t>PLANNING</t>
+  </si>
+  <si>
+    <t>PRESENT</t>
+  </si>
+  <si>
+    <t>PROD</t>
+  </si>
+  <si>
+    <t>Per authority matrix</t>
+  </si>
+  <si>
+    <t>Prepared Date</t>
+  </si>
+  <si>
+    <t>Process Owner</t>
+  </si>
+  <si>
+    <t>Purpose</t>
+  </si>
+  <si>
+    <t>QA</t>
+  </si>
+  <si>
+    <t>QMS</t>
+  </si>
+  <si>
+    <t>QUALITY</t>
+  </si>
+  <si>
+    <t>Quality Management System · Controlled Document</t>
+  </si>
+  <si>
+    <t>READ-AND-UNDERSTAND</t>
+  </si>
+  <si>
+    <t>RECALL</t>
+  </si>
+  <si>
+    <t>REGULATOR</t>
+  </si>
+  <si>
+    <t>REJECT</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>REPLACE</t>
+  </si>
+  <si>
+    <t>REQUIREMENT_CLASS</t>
+  </si>
+  <si>
+    <t>RESULT</t>
+  </si>
+  <si>
+    <t>RETURN</t>
+  </si>
+  <si>
+    <t>REVIEW_OUTCOME</t>
+  </si>
+  <si>
+    <t>REVISE</t>
+  </si>
+  <si>
+    <t>RISK</t>
+  </si>
+  <si>
+    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
+  </si>
+  <si>
+    <t>Reference Path or Link</t>
+  </si>
+  <si>
+    <t>Register Status</t>
+  </si>
+  <si>
+    <t>Related Record</t>
+  </si>
+  <si>
+    <t>Renewal Date</t>
+  </si>
+  <si>
+    <t>Retention / Archive Ref</t>
+  </si>
+  <si>
+    <t>Review Date</t>
+  </si>
+  <si>
+    <t>Review Owner</t>
+  </si>
+  <si>
+    <t>Review Period</t>
+  </si>
+  <si>
+    <t>Reviewed By</t>
+  </si>
+  <si>
+    <t>Reviewer</t>
+  </si>
+  <si>
+    <t>Revision</t>
+  </si>
+  <si>
+    <t>SAFETY</t>
+  </si>
+  <si>
+    <t>SALES</t>
+  </si>
+  <si>
+    <t>SECURITY</t>
+  </si>
+  <si>
+    <t>SHAREHOLDER</t>
+  </si>
+  <si>
+    <t>SHOP FLOOR</t>
+  </si>
+  <si>
+    <t>SOCIAL</t>
+  </si>
+  <si>
+    <t>SOP-801; WI-801 / WI-804; ANNEX-HR-001 + ANNEX-QMS-027 / 028</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>STRATEGIC</t>
+  </si>
+  <si>
+    <t>SUPERSEDED</t>
+  </si>
+  <si>
+    <t>SUPERVISED</t>
+  </si>
+  <si>
+    <t>SUPPLIER</t>
+  </si>
+  <si>
+    <t>SUSPENDED</t>
+  </si>
+  <si>
+    <t>SWOT</t>
+  </si>
+  <si>
+    <t>Skill or Certificate</t>
+  </si>
+  <si>
+    <t>Source Links</t>
+  </si>
+  <si>
+    <t>Source System</t>
+  </si>
+  <si>
+    <t>TEST</t>
+  </si>
+  <si>
+    <t>TRACEABILITY</t>
+  </si>
+  <si>
+    <t>TRAINING_METHOD</t>
+  </si>
+  <si>
+    <t>TRANSITION CUSTOMER</t>
+  </si>
+  <si>
+    <t>TRANSITION MARKET</t>
+  </si>
+  <si>
+    <t>TRANSITION REGULATORY</t>
+  </si>
+  <si>
+    <t>Trigger</t>
+  </si>
+  <si>
+    <t>UNDER REVIEW</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>V0</t>
+  </si>
+  <si>
+    <t>VALID</t>
+  </si>
+  <si>
+    <t>VND</t>
+  </si>
+  <si>
+    <t>VOID</t>
+  </si>
+  <si>
+    <t>WAREHOUSE</t>
+  </si>
+  <si>
+    <t>WHS</t>
+  </si>
+  <si>
+    <t>Window</t>
+  </si>
+  <si>
+    <t>YES</t>
+  </si>
+  <si>
+    <t>YES_NO</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -140,8 +778,13 @@
       <color rgb="001B3A6B"/>
       <sz val="14"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="007B4F00"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -198,8 +841,13 @@
         <fgColor rgb="000C2D48"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="145">
+  <borders count="148">
     <border>
       <left/>
       <right/>
@@ -1757,11 +2405,45 @@
       </top>
       <bottom/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="339">
+  <cellXfs count="342">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2640,6 +3322,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="128" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="145" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="146" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5411,67 +6102,67 @@
       <c r="BC36" s="248" t="n"/>
       <c r="BD36" s="248" t="n"/>
     </row>
-    <row r="37" ht="18" customHeight="1">
-      <c r="A37" s="291" t="inlineStr">
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="339" t="inlineStr">
         <is>
           <t>NOTICE: Keep one row per certification or requalification item. Record issue date, expiry date, current status, owner and the next action before the item becomes overdue.</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
-      <c r="J37" s="6" t="n"/>
-      <c r="K37" s="6" t="n"/>
-      <c r="L37" s="6" t="n"/>
-      <c r="M37" s="6" t="n"/>
-      <c r="N37" s="6" t="n"/>
-      <c r="O37" s="6" t="n"/>
-      <c r="P37" s="6" t="n"/>
-      <c r="Q37" s="6" t="n"/>
-      <c r="R37" s="6" t="n"/>
-      <c r="S37" s="6" t="n"/>
-      <c r="T37" s="6" t="n"/>
-      <c r="U37" s="6" t="n"/>
-      <c r="V37" s="6" t="n"/>
-      <c r="W37" s="6" t="n"/>
-      <c r="X37" s="6" t="n"/>
-      <c r="Y37" s="6" t="n"/>
-      <c r="Z37" s="6" t="n"/>
-      <c r="AA37" s="6" t="n"/>
-      <c r="AB37" s="6" t="n"/>
-      <c r="AC37" s="6" t="n"/>
-      <c r="AD37" s="6" t="n"/>
-      <c r="AE37" s="6" t="n"/>
-      <c r="AF37" s="6" t="n"/>
-      <c r="AG37" s="6" t="n"/>
-      <c r="AH37" s="6" t="n"/>
-      <c r="AI37" s="6" t="n"/>
-      <c r="AJ37" s="6" t="n"/>
-      <c r="AK37" s="6" t="n"/>
-      <c r="AL37" s="6" t="n"/>
-      <c r="AM37" s="6" t="n"/>
-      <c r="AN37" s="6" t="n"/>
-      <c r="AO37" s="6" t="n"/>
-      <c r="AP37" s="6" t="n"/>
-      <c r="AQ37" s="6" t="n"/>
-      <c r="AR37" s="6" t="n"/>
-      <c r="AS37" s="6" t="n"/>
-      <c r="AT37" s="6" t="n"/>
-      <c r="AU37" s="6" t="n"/>
-      <c r="AV37" s="6" t="n"/>
-      <c r="AW37" s="6" t="n"/>
-      <c r="AX37" s="6" t="n"/>
-      <c r="AY37" s="6" t="n"/>
-      <c r="AZ37" s="6" t="n"/>
-      <c r="BA37" s="6" t="n"/>
-      <c r="BB37" s="6" t="n"/>
-      <c r="BC37" s="6" t="n"/>
-      <c r="BD37" s="7" t="n"/>
+      <c r="B37" s="340" t="n"/>
+      <c r="C37" s="340" t="n"/>
+      <c r="D37" s="340" t="n"/>
+      <c r="E37" s="340" t="n"/>
+      <c r="F37" s="340" t="n"/>
+      <c r="G37" s="340" t="n"/>
+      <c r="H37" s="340" t="n"/>
+      <c r="I37" s="340" t="n"/>
+      <c r="J37" s="340" t="n"/>
+      <c r="K37" s="340" t="n"/>
+      <c r="L37" s="340" t="n"/>
+      <c r="M37" s="340" t="n"/>
+      <c r="N37" s="340" t="n"/>
+      <c r="O37" s="340" t="n"/>
+      <c r="P37" s="340" t="n"/>
+      <c r="Q37" s="340" t="n"/>
+      <c r="R37" s="340" t="n"/>
+      <c r="S37" s="340" t="n"/>
+      <c r="T37" s="340" t="n"/>
+      <c r="U37" s="340" t="n"/>
+      <c r="V37" s="340" t="n"/>
+      <c r="W37" s="340" t="n"/>
+      <c r="X37" s="340" t="n"/>
+      <c r="Y37" s="340" t="n"/>
+      <c r="Z37" s="340" t="n"/>
+      <c r="AA37" s="340" t="n"/>
+      <c r="AB37" s="340" t="n"/>
+      <c r="AC37" s="340" t="n"/>
+      <c r="AD37" s="340" t="n"/>
+      <c r="AE37" s="340" t="n"/>
+      <c r="AF37" s="340" t="n"/>
+      <c r="AG37" s="340" t="n"/>
+      <c r="AH37" s="340" t="n"/>
+      <c r="AI37" s="340" t="n"/>
+      <c r="AJ37" s="340" t="n"/>
+      <c r="AK37" s="340" t="n"/>
+      <c r="AL37" s="340" t="n"/>
+      <c r="AM37" s="340" t="n"/>
+      <c r="AN37" s="340" t="n"/>
+      <c r="AO37" s="340" t="n"/>
+      <c r="AP37" s="340" t="n"/>
+      <c r="AQ37" s="340" t="n"/>
+      <c r="AR37" s="340" t="n"/>
+      <c r="AS37" s="340" t="n"/>
+      <c r="AT37" s="340" t="n"/>
+      <c r="AU37" s="340" t="n"/>
+      <c r="AV37" s="340" t="n"/>
+      <c r="AW37" s="340" t="n"/>
+      <c r="AX37" s="340" t="n"/>
+      <c r="AY37" s="340" t="n"/>
+      <c r="AZ37" s="340" t="n"/>
+      <c r="BA37" s="340" t="n"/>
+      <c r="BB37" s="340" t="n"/>
+      <c r="BC37" s="340" t="n"/>
+      <c r="BD37" s="341" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
@@ -847,7 +847,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="148">
+  <borders count="153">
     <border>
       <left/>
       <right/>
@@ -2438,6 +2438,64 @@
       <bottom style="thin">
         <color rgb="00F9A825"/>
       </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00F9A825"/>
+      </left>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00F9A825"/>
+      </right>
+      <top style="thin">
+        <color rgb="00F9A825"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00F9A825"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">

--- a/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
@@ -24,644 +24,6 @@
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="211">
-  <si>
-    <t>  1. CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>  1. REFERENCE INFORMATION</t>
-  </si>
-  <si>
-    <t>  2. ACTIVE LOG TABLE</t>
-  </si>
-  <si>
-    <t>  3. PERIODIC REVIEW / CLOSURE</t>
-  </si>
-  <si>
-    <t>  4. PERIODIC REVIEW SIGN-OFF</t>
-  </si>
-  <si>
-    <t>  EXPIRY CONTROL WINDOWS</t>
-  </si>
-  <si>
-    <t>  REFERENCE / SOURCE CONTEXT</t>
-  </si>
-  <si>
-    <t>  SUPPORT TABLE</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$14)+1</t>
-  </si>
-  <si>
-    <t>ABSENT</t>
-  </si>
-  <si>
-    <t>ACCEPT</t>
-  </si>
-  <si>
-    <t>ACCEPT WITH ACTION</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>ATTENDANCE_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZATION_STATUS</t>
-  </si>
-  <si>
-    <t>AUTHORIZED</t>
-  </si>
-  <si>
-    <t>AWARE</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved By</t>
-  </si>
-  <si>
-    <t>Boundary / SoR</t>
-  </si>
-  <si>
-    <t>CERTIFICATION BODY</t>
-  </si>
-  <si>
-    <t>CERTIFICATION TRACKING LOG</t>
-  </si>
-  <si>
-    <t>CERTIFICATION TRACKING LOG — CONTROLLED LOOKUP LISTS</t>
-  </si>
-  <si>
-    <t>CERTIFICATION TRACKING LOG — EVIDENCE REFERENCE REGISTER</t>
-  </si>
-  <si>
-    <t>CERTIFICATION TRACKING LOG — EXPIRY QUEUE / FOLLOW-UP</t>
-  </si>
-  <si>
-    <t>CERT_STATUS</t>
-  </si>
-  <si>
-    <t>CLASSROOM</t>
-  </si>
-  <si>
-    <t>CLIMATE_SCENARIO</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>COACHING</t>
-  </si>
-  <si>
-    <t>COMBINED</t>
-  </si>
-  <si>
-    <t>COMMUNITY</t>
-  </si>
-  <si>
-    <t>COMPETENCY_LEVEL</t>
-  </si>
-  <si>
-    <t>COMPLIANCE</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>CONTEXT_CLASS</t>
-  </si>
-  <si>
-    <t>CONTRACTUAL</t>
-  </si>
-  <si>
-    <t>COPY_ACTION</t>
-  </si>
-  <si>
-    <t>CRITICAL</t>
-  </si>
-  <si>
-    <t>CSR_CLASS</t>
-  </si>
-  <si>
-    <t>CURRENCY</t>
-  </si>
-  <si>
-    <t>CUSTOMER</t>
-  </si>
-  <si>
-    <t>Cert Status</t>
-  </si>
-  <si>
-    <t>Certification Log ID</t>
-  </si>
-  <si>
-    <t>Certification tracking log monitors renewals / expiry and status; references certificates rather than reassessing competence itself.</t>
-  </si>
-  <si>
-    <t>Comments</t>
-  </si>
-  <si>
-    <t>Competency Level</t>
-  </si>
-  <si>
-    <t>DECISION</t>
-  </si>
-  <si>
-    <t>DELIVERY</t>
-  </si>
-  <si>
-    <t>DEPT</t>
-  </si>
-  <si>
-    <t>DESTROY</t>
-  </si>
-  <si>
-    <t>DEVELOPMENT_PRIORITY</t>
-  </si>
-  <si>
-    <t>DOC_STATUS</t>
-  </si>
-  <si>
-    <t>DRAFT</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Department / Scope</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>EFFECTIVE</t>
-  </si>
-  <si>
-    <t>EMPLOYEE</t>
-  </si>
-  <si>
-    <t>ENG</t>
-  </si>
-  <si>
-    <t>ENVIRONMENT</t>
-  </si>
-  <si>
-    <t>ENVIRONMENTAL</t>
-  </si>
-  <si>
-    <t>ESG</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>EXCUSED</t>
-  </si>
-  <si>
-    <t>EXPIRED</t>
-  </si>
-  <si>
-    <t>EXPIRING</t>
-  </si>
-  <si>
-    <t>EXTERNAL COURSE</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Employee ID</t>
-  </si>
-  <si>
-    <t>Employee Name</t>
-  </si>
-  <si>
-    <t>Evidence Folder Ref</t>
-  </si>
-  <si>
-    <t>Evidence ID</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>Excel Table — certification tracker (freeze / filter required)</t>
-  </si>
-  <si>
-    <t>Expiring Items</t>
-  </si>
-  <si>
-    <t>Expiry Date</t>
-  </si>
-  <si>
-    <t>FACILITY</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FINANCE</t>
-  </si>
-  <si>
-    <t>FRM-806</t>
-  </si>
-  <si>
-    <t>Final Status</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HIGH</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>HR</t>
-  </si>
-  <si>
-    <t>HR + Department Manager</t>
-  </si>
-  <si>
-    <t>HSE</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>INCIDENT_CLASS</t>
-  </si>
-  <si>
-    <t>INDEPENDENT</t>
-  </si>
-  <si>
-    <t>INSPECTION</t>
-  </si>
-  <si>
-    <t>INSURANCE</t>
-  </si>
-  <si>
-    <t>INTERNAL</t>
-  </si>
-  <si>
-    <t>ISSUE</t>
-  </si>
-  <si>
-    <t>ISSUE_ACTION</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>Issue Date</t>
-  </si>
-  <si>
-    <t>JPY</t>
-  </si>
-  <si>
-    <t>LATE</t>
-  </si>
-  <si>
-    <t>LEGAL</t>
-  </si>
-  <si>
-    <t>LIGHTING_AREA</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>M365 evidence / shared workbook</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
-    <t>MEETING ROOM</t>
-  </si>
-  <si>
-    <t>MGT</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NOT AUTHORIZED</t>
-  </si>
-  <si>
-    <t>NOT TRAINED</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
-  </si>
-  <si>
-    <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
-  </si>
-  <si>
-    <t>NOTICE: Keep one row per certification or requalification item. Record issue date, expiry date, current status, owner and the next action before the item becomes overdue.</t>
-  </si>
-  <si>
-    <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
-  </si>
-  <si>
-    <t>Name / Signature / Date</t>
-  </si>
-  <si>
-    <t>Next Action</t>
-  </si>
-  <si>
-    <t>No.</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-  <si>
-    <t>OBSERVATION</t>
-  </si>
-  <si>
-    <t>OBSOLETE</t>
-  </si>
-  <si>
-    <t>OFFICE</t>
-  </si>
-  <si>
-    <t>OJT</t>
-  </si>
-  <si>
-    <t>ON HOLD</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>OTHER</t>
-  </si>
-  <si>
-    <t>OUTDOOR</t>
-  </si>
-  <si>
-    <t>OWNER</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>PACKAGING</t>
-  </si>
-  <si>
-    <t>PARTY_TYPE</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PESTLE</t>
-  </si>
-  <si>
-    <t>PHYSICAL ACUTE</t>
-  </si>
-  <si>
-    <t>PHYSICAL CHRONIC</t>
-  </si>
-  <si>
-    <t>PLANNED</t>
-  </si>
-  <si>
-    <t>PLANNING</t>
-  </si>
-  <si>
-    <t>PRESENT</t>
-  </si>
-  <si>
-    <t>PROD</t>
-  </si>
-  <si>
-    <t>Per authority matrix</t>
-  </si>
-  <si>
-    <t>Prepared Date</t>
-  </si>
-  <si>
-    <t>Process Owner</t>
-  </si>
-  <si>
-    <t>Purpose</t>
-  </si>
-  <si>
-    <t>QA</t>
-  </si>
-  <si>
-    <t>QMS</t>
-  </si>
-  <si>
-    <t>QUALITY</t>
-  </si>
-  <si>
-    <t>Quality Management System · Controlled Document</t>
-  </si>
-  <si>
-    <t>READ-AND-UNDERSTAND</t>
-  </si>
-  <si>
-    <t>RECALL</t>
-  </si>
-  <si>
-    <t>REGULATOR</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>REJECTED</t>
-  </si>
-  <si>
-    <t>REPLACE</t>
-  </si>
-  <si>
-    <t>REQUIREMENT_CLASS</t>
-  </si>
-  <si>
-    <t>RESULT</t>
-  </si>
-  <si>
-    <t>RETURN</t>
-  </si>
-  <si>
-    <t>REVIEW_OUTCOME</t>
-  </si>
-  <si>
-    <t>REVISE</t>
-  </si>
-  <si>
-    <t>RISK</t>
-  </si>
-  <si>
-    <t>Record traceable evidence references only; do not duplicate system-owned master data.</t>
-  </si>
-  <si>
-    <t>Reference Path or Link</t>
-  </si>
-  <si>
-    <t>Register Status</t>
-  </si>
-  <si>
-    <t>Related Record</t>
-  </si>
-  <si>
-    <t>Renewal Date</t>
-  </si>
-  <si>
-    <t>Retention / Archive Ref</t>
-  </si>
-  <si>
-    <t>Review Date</t>
-  </si>
-  <si>
-    <t>Review Owner</t>
-  </si>
-  <si>
-    <t>Review Period</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Reviewer</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SAFETY</t>
-  </si>
-  <si>
-    <t>SALES</t>
-  </si>
-  <si>
-    <t>SECURITY</t>
-  </si>
-  <si>
-    <t>SHAREHOLDER</t>
-  </si>
-  <si>
-    <t>SHOP FLOOR</t>
-  </si>
-  <si>
-    <t>SOCIAL</t>
-  </si>
-  <si>
-    <t>SOP-801; WI-801 / WI-804; ANNEX-HR-001 + ANNEX-QMS-027 / 028</t>
-  </si>
-  <si>
-    <t>STATUS</t>
-  </si>
-  <si>
-    <t>STRATEGIC</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>SUPERVISED</t>
-  </si>
-  <si>
-    <t>SUPPLIER</t>
-  </si>
-  <si>
-    <t>SUSPENDED</t>
-  </si>
-  <si>
-    <t>SWOT</t>
-  </si>
-  <si>
-    <t>Skill or Certificate</t>
-  </si>
-  <si>
-    <t>Source Links</t>
-  </si>
-  <si>
-    <t>Source System</t>
-  </si>
-  <si>
-    <t>TEST</t>
-  </si>
-  <si>
-    <t>TRACEABILITY</t>
-  </si>
-  <si>
-    <t>TRAINING_METHOD</t>
-  </si>
-  <si>
-    <t>TRANSITION CUSTOMER</t>
-  </si>
-  <si>
-    <t>TRANSITION MARKET</t>
-  </si>
-  <si>
-    <t>TRANSITION REGULATORY</t>
-  </si>
-  <si>
-    <t>Trigger</t>
-  </si>
-  <si>
-    <t>UNDER REVIEW</t>
-  </si>
-  <si>
-    <t>USD</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VALID</t>
-  </si>
-  <si>
-    <t>VND</t>
-  </si>
-  <si>
-    <t>VOID</t>
-  </si>
-  <si>
-    <t>WAREHOUSE</t>
-  </si>
-  <si>
-    <t>WHS</t>
-  </si>
-  <si>
-    <t>Window</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>YES_NO</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -847,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="153">
+  <borders count="155">
     <border>
       <left/>
       <right/>
@@ -2497,11 +1859,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="000078D4"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="342">
+  <cellXfs count="379">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3389,6 +2775,97 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="147" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="115" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="116" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="117" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="131" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="119" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="134" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="133" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="129" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="130" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="124" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="135" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="124" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="153" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3471,11 +2948,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3489,9 +2966,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3504,11 +2978,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3522,9 +2996,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3537,11 +3008,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3555,9 +3026,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3570,11 +3038,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -3588,9 +3056,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3948,7 +3413,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="277" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -3960,7 +3425,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="190" t="inlineStr">
+      <c r="L1" s="377" t="inlineStr">
         <is>
           <t>CERTIFICATION TRACKING LOG</t>
         </is>
@@ -3994,7 +3459,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="278" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -4019,279 +3484,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="281" t="inlineStr">
+      <c r="A2" s="342" t="n"/>
+      <c r="B2" s="343" t="n"/>
+      <c r="C2" s="343" t="n"/>
+      <c r="D2" s="343" t="n"/>
+      <c r="E2" s="343" t="n"/>
+      <c r="F2" s="343" t="n"/>
+      <c r="G2" s="343" t="n"/>
+      <c r="H2" s="343" t="n"/>
+      <c r="I2" s="343" t="n"/>
+      <c r="J2" s="343" t="n"/>
+      <c r="K2" s="344" t="n"/>
+      <c r="L2" s="343" t="n"/>
+      <c r="M2" s="343" t="n"/>
+      <c r="N2" s="343" t="n"/>
+      <c r="O2" s="343" t="n"/>
+      <c r="P2" s="343" t="n"/>
+      <c r="Q2" s="343" t="n"/>
+      <c r="R2" s="343" t="n"/>
+      <c r="S2" s="343" t="n"/>
+      <c r="T2" s="343" t="n"/>
+      <c r="U2" s="343" t="n"/>
+      <c r="V2" s="343" t="n"/>
+      <c r="W2" s="343" t="n"/>
+      <c r="X2" s="343" t="n"/>
+      <c r="Y2" s="343" t="n"/>
+      <c r="Z2" s="343" t="n"/>
+      <c r="AA2" s="343" t="n"/>
+      <c r="AB2" s="343" t="n"/>
+      <c r="AC2" s="343" t="n"/>
+      <c r="AD2" s="343" t="n"/>
+      <c r="AE2" s="343" t="n"/>
+      <c r="AF2" s="343" t="n"/>
+      <c r="AG2" s="343" t="n"/>
+      <c r="AH2" s="343" t="n"/>
+      <c r="AI2" s="343" t="n"/>
+      <c r="AJ2" s="343" t="n"/>
+      <c r="AK2" s="343" t="n"/>
+      <c r="AL2" s="343" t="n"/>
+      <c r="AM2" s="343" t="n"/>
+      <c r="AN2" s="343" t="n"/>
+      <c r="AO2" s="343" t="n"/>
+      <c r="AP2" s="344" t="n"/>
+      <c r="AQ2" s="345" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="282" t="n"/>
-      <c r="AS2" s="282" t="n"/>
-      <c r="AT2" s="282" t="n"/>
-      <c r="AU2" s="282" t="n"/>
-      <c r="AV2" s="283" t="n"/>
-      <c r="AW2" s="284" t="inlineStr">
+      <c r="AR2" s="346" t="n"/>
+      <c r="AS2" s="346" t="n"/>
+      <c r="AT2" s="346" t="n"/>
+      <c r="AU2" s="346" t="n"/>
+      <c r="AV2" s="347" t="n"/>
+      <c r="AW2" s="348" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="282" t="n"/>
-      <c r="AY2" s="282" t="n"/>
-      <c r="AZ2" s="282" t="n"/>
-      <c r="BA2" s="282" t="n"/>
-      <c r="BB2" s="282" t="n"/>
-      <c r="BC2" s="282" t="n"/>
-      <c r="BD2" s="285" t="n"/>
+      <c r="AX2" s="349" t="n"/>
+      <c r="AY2" s="349" t="n"/>
+      <c r="AZ2" s="349" t="n"/>
+      <c r="BA2" s="349" t="n"/>
+      <c r="BB2" s="349" t="n"/>
+      <c r="BC2" s="349" t="n"/>
+      <c r="BD2" s="350" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="281" t="inlineStr">
+      <c r="A3" s="351" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="352" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="352" t="n"/>
+      <c r="AQ3" s="353" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="282" t="n"/>
-      <c r="AS3" s="282" t="n"/>
-      <c r="AT3" s="282" t="n"/>
-      <c r="AU3" s="282" t="n"/>
-      <c r="AV3" s="283" t="n"/>
-      <c r="AW3" s="284" t="inlineStr">
+      <c r="AR3" s="354" t="n"/>
+      <c r="AS3" s="354" t="n"/>
+      <c r="AT3" s="354" t="n"/>
+      <c r="AU3" s="354" t="n"/>
+      <c r="AV3" s="355" t="n"/>
+      <c r="AW3" s="250" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="282" t="n"/>
-      <c r="AY3" s="282" t="n"/>
-      <c r="AZ3" s="282" t="n"/>
-      <c r="BA3" s="282" t="n"/>
-      <c r="BB3" s="282" t="n"/>
-      <c r="BC3" s="282" t="n"/>
-      <c r="BD3" s="285" t="n"/>
+      <c r="AX3" s="356" t="n"/>
+      <c r="AY3" s="356" t="n"/>
+      <c r="AZ3" s="356" t="n"/>
+      <c r="BA3" s="356" t="n"/>
+      <c r="BB3" s="356" t="n"/>
+      <c r="BC3" s="356" t="n"/>
+      <c r="BD3" s="357" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="202" t="inlineStr">
+      <c r="A4" s="351" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="352" t="n"/>
+      <c r="L4" s="358" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="281" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="352" t="n"/>
+      <c r="AQ4" s="353" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="282" t="n"/>
-      <c r="AS4" s="282" t="n"/>
-      <c r="AT4" s="282" t="n"/>
-      <c r="AU4" s="282" t="n"/>
-      <c r="AV4" s="283" t="n"/>
-      <c r="AW4" s="284" t="inlineStr">
+      <c r="AR4" s="354" t="n"/>
+      <c r="AS4" s="354" t="n"/>
+      <c r="AT4" s="354" t="n"/>
+      <c r="AU4" s="354" t="n"/>
+      <c r="AV4" s="355" t="n"/>
+      <c r="AW4" s="250" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="282" t="n"/>
-      <c r="AY4" s="282" t="n"/>
-      <c r="AZ4" s="282" t="n"/>
-      <c r="BA4" s="282" t="n"/>
-      <c r="BB4" s="282" t="n"/>
-      <c r="BC4" s="282" t="n"/>
-      <c r="BD4" s="285" t="n"/>
+      <c r="AX4" s="356" t="n"/>
+      <c r="AY4" s="356" t="n"/>
+      <c r="AZ4" s="356" t="n"/>
+      <c r="BA4" s="356" t="n"/>
+      <c r="BB4" s="356" t="n"/>
+      <c r="BC4" s="356" t="n"/>
+      <c r="BD4" s="357" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="351" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="352" t="n"/>
+      <c r="L5" s="359" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="286" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="352" t="n"/>
+      <c r="AQ5" s="353" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="287" t="n"/>
-      <c r="AS5" s="287" t="n"/>
-      <c r="AT5" s="287" t="n"/>
-      <c r="AU5" s="287" t="n"/>
-      <c r="AV5" s="288" t="n"/>
-      <c r="AW5" s="289" t="inlineStr">
+      <c r="AR5" s="354" t="n"/>
+      <c r="AS5" s="354" t="n"/>
+      <c r="AT5" s="354" t="n"/>
+      <c r="AU5" s="354" t="n"/>
+      <c r="AV5" s="355" t="n"/>
+      <c r="AW5" s="250" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="287" t="n"/>
-      <c r="AY5" s="287" t="n"/>
-      <c r="AZ5" s="287" t="n"/>
-      <c r="BA5" s="287" t="n"/>
-      <c r="BB5" s="287" t="n"/>
-      <c r="BC5" s="287" t="n"/>
-      <c r="BD5" s="290" t="n"/>
+      <c r="AX5" s="356" t="n"/>
+      <c r="AY5" s="356" t="n"/>
+      <c r="AZ5" s="356" t="n"/>
+      <c r="BA5" s="356" t="n"/>
+      <c r="BB5" s="356" t="n"/>
+      <c r="BC5" s="356" t="n"/>
+      <c r="BD5" s="357" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="211" t="n"/>
-      <c r="B6" s="211" t="n"/>
-      <c r="C6" s="211" t="n"/>
-      <c r="D6" s="211" t="n"/>
-      <c r="E6" s="211" t="n"/>
-      <c r="F6" s="211" t="n"/>
-      <c r="G6" s="211" t="n"/>
-      <c r="H6" s="211" t="n"/>
-      <c r="I6" s="211" t="n"/>
-      <c r="J6" s="211" t="n"/>
-      <c r="K6" s="211" t="n"/>
-      <c r="L6" s="211" t="n"/>
-      <c r="M6" s="211" t="n"/>
-      <c r="N6" s="211" t="n"/>
-      <c r="O6" s="211" t="n"/>
-      <c r="P6" s="211" t="n"/>
-      <c r="Q6" s="211" t="n"/>
-      <c r="R6" s="211" t="n"/>
-      <c r="S6" s="211" t="n"/>
-      <c r="T6" s="211" t="n"/>
-      <c r="U6" s="211" t="n"/>
-      <c r="V6" s="211" t="n"/>
-      <c r="W6" s="211" t="n"/>
-      <c r="X6" s="211" t="n"/>
-      <c r="Y6" s="211" t="n"/>
-      <c r="Z6" s="211" t="n"/>
-      <c r="AA6" s="211" t="n"/>
-      <c r="AB6" s="211" t="n"/>
-      <c r="AC6" s="211" t="n"/>
-      <c r="AD6" s="211" t="n"/>
-      <c r="AE6" s="211" t="n"/>
-      <c r="AF6" s="211" t="n"/>
-      <c r="AG6" s="211" t="n"/>
-      <c r="AH6" s="211" t="n"/>
-      <c r="AI6" s="211" t="n"/>
-      <c r="AJ6" s="211" t="n"/>
-      <c r="AK6" s="211" t="n"/>
-      <c r="AL6" s="211" t="n"/>
-      <c r="AM6" s="211" t="n"/>
-      <c r="AN6" s="211" t="n"/>
-      <c r="AO6" s="211" t="n"/>
-      <c r="AP6" s="211" t="n"/>
-      <c r="AQ6" s="211" t="n"/>
-      <c r="AR6" s="211" t="n"/>
-      <c r="AS6" s="211" t="n"/>
-      <c r="AT6" s="211" t="n"/>
-      <c r="AU6" s="211" t="n"/>
-      <c r="AV6" s="211" t="n"/>
-      <c r="AW6" s="211" t="n"/>
-      <c r="AX6" s="211" t="n"/>
-      <c r="AY6" s="211" t="n"/>
-      <c r="AZ6" s="211" t="n"/>
-      <c r="BA6" s="211" t="n"/>
-      <c r="BB6" s="211" t="n"/>
-      <c r="BC6" s="211" t="n"/>
-      <c r="BD6" s="211" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="360" t="n"/>
+      <c r="B6" s="361" t="n"/>
+      <c r="C6" s="361" t="n"/>
+      <c r="D6" s="361" t="n"/>
+      <c r="E6" s="361" t="n"/>
+      <c r="F6" s="361" t="n"/>
+      <c r="G6" s="361" t="n"/>
+      <c r="H6" s="361" t="n"/>
+      <c r="I6" s="361" t="n"/>
+      <c r="J6" s="361" t="n"/>
+      <c r="K6" s="362" t="n"/>
+      <c r="L6" s="361" t="n"/>
+      <c r="M6" s="361" t="n"/>
+      <c r="N6" s="361" t="n"/>
+      <c r="O6" s="361" t="n"/>
+      <c r="P6" s="361" t="n"/>
+      <c r="Q6" s="361" t="n"/>
+      <c r="R6" s="361" t="n"/>
+      <c r="S6" s="361" t="n"/>
+      <c r="T6" s="361" t="n"/>
+      <c r="U6" s="361" t="n"/>
+      <c r="V6" s="361" t="n"/>
+      <c r="W6" s="361" t="n"/>
+      <c r="X6" s="361" t="n"/>
+      <c r="Y6" s="361" t="n"/>
+      <c r="Z6" s="361" t="n"/>
+      <c r="AA6" s="361" t="n"/>
+      <c r="AB6" s="361" t="n"/>
+      <c r="AC6" s="361" t="n"/>
+      <c r="AD6" s="361" t="n"/>
+      <c r="AE6" s="361" t="n"/>
+      <c r="AF6" s="361" t="n"/>
+      <c r="AG6" s="361" t="n"/>
+      <c r="AH6" s="361" t="n"/>
+      <c r="AI6" s="361" t="n"/>
+      <c r="AJ6" s="361" t="n"/>
+      <c r="AK6" s="361" t="n"/>
+      <c r="AL6" s="361" t="n"/>
+      <c r="AM6" s="361" t="n"/>
+      <c r="AN6" s="361" t="n"/>
+      <c r="AO6" s="361" t="n"/>
+      <c r="AP6" s="362" t="n"/>
+      <c r="AQ6" s="363" t="n"/>
+      <c r="AR6" s="363" t="n"/>
+      <c r="AS6" s="363" t="n"/>
+      <c r="AT6" s="363" t="n"/>
+      <c r="AU6" s="363" t="n"/>
+      <c r="AV6" s="364" t="n"/>
+      <c r="AW6" s="365" t="n"/>
+      <c r="AX6" s="365" t="n"/>
+      <c r="AY6" s="365" t="n"/>
+      <c r="AZ6" s="365" t="n"/>
+      <c r="BA6" s="365" t="n"/>
+      <c r="BB6" s="365" t="n"/>
+      <c r="BC6" s="365" t="n"/>
+      <c r="BD6" s="366" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. REFERENCE INFORMATION</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="367" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="292" t="inlineStr">
@@ -6161,66 +5739,66 @@
       <c r="BD36" s="248" t="n"/>
     </row>
     <row r="37" ht="26" customHeight="1">
-      <c r="A37" s="339" t="inlineStr">
+      <c r="A37" s="267" t="inlineStr">
         <is>
           <t>NOTICE: Keep one row per certification or requalification item. Record issue date, expiry date, current status, owner and the next action before the item becomes overdue.</t>
         </is>
       </c>
-      <c r="B37" s="340" t="n"/>
-      <c r="C37" s="340" t="n"/>
-      <c r="D37" s="340" t="n"/>
-      <c r="E37" s="340" t="n"/>
-      <c r="F37" s="340" t="n"/>
-      <c r="G37" s="340" t="n"/>
-      <c r="H37" s="340" t="n"/>
-      <c r="I37" s="340" t="n"/>
-      <c r="J37" s="340" t="n"/>
-      <c r="K37" s="340" t="n"/>
-      <c r="L37" s="340" t="n"/>
-      <c r="M37" s="340" t="n"/>
-      <c r="N37" s="340" t="n"/>
-      <c r="O37" s="340" t="n"/>
-      <c r="P37" s="340" t="n"/>
-      <c r="Q37" s="340" t="n"/>
-      <c r="R37" s="340" t="n"/>
-      <c r="S37" s="340" t="n"/>
-      <c r="T37" s="340" t="n"/>
-      <c r="U37" s="340" t="n"/>
-      <c r="V37" s="340" t="n"/>
-      <c r="W37" s="340" t="n"/>
-      <c r="X37" s="340" t="n"/>
-      <c r="Y37" s="340" t="n"/>
-      <c r="Z37" s="340" t="n"/>
-      <c r="AA37" s="340" t="n"/>
-      <c r="AB37" s="340" t="n"/>
-      <c r="AC37" s="340" t="n"/>
-      <c r="AD37" s="340" t="n"/>
-      <c r="AE37" s="340" t="n"/>
-      <c r="AF37" s="340" t="n"/>
-      <c r="AG37" s="340" t="n"/>
-      <c r="AH37" s="340" t="n"/>
-      <c r="AI37" s="340" t="n"/>
-      <c r="AJ37" s="340" t="n"/>
-      <c r="AK37" s="340" t="n"/>
-      <c r="AL37" s="340" t="n"/>
-      <c r="AM37" s="340" t="n"/>
-      <c r="AN37" s="340" t="n"/>
-      <c r="AO37" s="340" t="n"/>
-      <c r="AP37" s="340" t="n"/>
-      <c r="AQ37" s="340" t="n"/>
-      <c r="AR37" s="340" t="n"/>
-      <c r="AS37" s="340" t="n"/>
-      <c r="AT37" s="340" t="n"/>
-      <c r="AU37" s="340" t="n"/>
-      <c r="AV37" s="340" t="n"/>
-      <c r="AW37" s="340" t="n"/>
-      <c r="AX37" s="340" t="n"/>
-      <c r="AY37" s="340" t="n"/>
-      <c r="AZ37" s="340" t="n"/>
-      <c r="BA37" s="340" t="n"/>
-      <c r="BB37" s="340" t="n"/>
-      <c r="BC37" s="340" t="n"/>
-      <c r="BD37" s="341" t="n"/>
+      <c r="B37" s="368" t="n"/>
+      <c r="C37" s="368" t="n"/>
+      <c r="D37" s="368" t="n"/>
+      <c r="E37" s="368" t="n"/>
+      <c r="F37" s="368" t="n"/>
+      <c r="G37" s="368" t="n"/>
+      <c r="H37" s="368" t="n"/>
+      <c r="I37" s="368" t="n"/>
+      <c r="J37" s="368" t="n"/>
+      <c r="K37" s="368" t="n"/>
+      <c r="L37" s="368" t="n"/>
+      <c r="M37" s="368" t="n"/>
+      <c r="N37" s="368" t="n"/>
+      <c r="O37" s="368" t="n"/>
+      <c r="P37" s="368" t="n"/>
+      <c r="Q37" s="368" t="n"/>
+      <c r="R37" s="368" t="n"/>
+      <c r="S37" s="368" t="n"/>
+      <c r="T37" s="368" t="n"/>
+      <c r="U37" s="368" t="n"/>
+      <c r="V37" s="368" t="n"/>
+      <c r="W37" s="368" t="n"/>
+      <c r="X37" s="368" t="n"/>
+      <c r="Y37" s="368" t="n"/>
+      <c r="Z37" s="368" t="n"/>
+      <c r="AA37" s="368" t="n"/>
+      <c r="AB37" s="368" t="n"/>
+      <c r="AC37" s="368" t="n"/>
+      <c r="AD37" s="368" t="n"/>
+      <c r="AE37" s="368" t="n"/>
+      <c r="AF37" s="368" t="n"/>
+      <c r="AG37" s="368" t="n"/>
+      <c r="AH37" s="368" t="n"/>
+      <c r="AI37" s="368" t="n"/>
+      <c r="AJ37" s="368" t="n"/>
+      <c r="AK37" s="368" t="n"/>
+      <c r="AL37" s="368" t="n"/>
+      <c r="AM37" s="368" t="n"/>
+      <c r="AN37" s="368" t="n"/>
+      <c r="AO37" s="368" t="n"/>
+      <c r="AP37" s="368" t="n"/>
+      <c r="AQ37" s="368" t="n"/>
+      <c r="AR37" s="368" t="n"/>
+      <c r="AS37" s="368" t="n"/>
+      <c r="AT37" s="368" t="n"/>
+      <c r="AU37" s="368" t="n"/>
+      <c r="AV37" s="368" t="n"/>
+      <c r="AW37" s="368" t="n"/>
+      <c r="AX37" s="368" t="n"/>
+      <c r="AY37" s="368" t="n"/>
+      <c r="AZ37" s="368" t="n"/>
+      <c r="BA37" s="368" t="n"/>
+      <c r="BB37" s="368" t="n"/>
+      <c r="BC37" s="368" t="n"/>
+      <c r="BD37" s="369" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1"/>
     <row r="39" ht="20" customHeight="1"/>
@@ -6814,7 +6392,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="277" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -6826,7 +6404,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="190" t="inlineStr">
+      <c r="L1" s="377" t="inlineStr">
         <is>
           <t>CERTIFICATION TRACKING LOG — EXPIRY QUEUE / FOLLOW-UP</t>
         </is>
@@ -6860,7 +6438,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="278" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -6885,279 +6463,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="281" t="inlineStr">
+      <c r="A2" s="342" t="n"/>
+      <c r="B2" s="343" t="n"/>
+      <c r="C2" s="343" t="n"/>
+      <c r="D2" s="343" t="n"/>
+      <c r="E2" s="343" t="n"/>
+      <c r="F2" s="343" t="n"/>
+      <c r="G2" s="343" t="n"/>
+      <c r="H2" s="343" t="n"/>
+      <c r="I2" s="343" t="n"/>
+      <c r="J2" s="343" t="n"/>
+      <c r="K2" s="344" t="n"/>
+      <c r="L2" s="343" t="n"/>
+      <c r="M2" s="343" t="n"/>
+      <c r="N2" s="343" t="n"/>
+      <c r="O2" s="343" t="n"/>
+      <c r="P2" s="343" t="n"/>
+      <c r="Q2" s="343" t="n"/>
+      <c r="R2" s="343" t="n"/>
+      <c r="S2" s="343" t="n"/>
+      <c r="T2" s="343" t="n"/>
+      <c r="U2" s="343" t="n"/>
+      <c r="V2" s="343" t="n"/>
+      <c r="W2" s="343" t="n"/>
+      <c r="X2" s="343" t="n"/>
+      <c r="Y2" s="343" t="n"/>
+      <c r="Z2" s="343" t="n"/>
+      <c r="AA2" s="343" t="n"/>
+      <c r="AB2" s="343" t="n"/>
+      <c r="AC2" s="343" t="n"/>
+      <c r="AD2" s="343" t="n"/>
+      <c r="AE2" s="343" t="n"/>
+      <c r="AF2" s="343" t="n"/>
+      <c r="AG2" s="343" t="n"/>
+      <c r="AH2" s="343" t="n"/>
+      <c r="AI2" s="343" t="n"/>
+      <c r="AJ2" s="343" t="n"/>
+      <c r="AK2" s="343" t="n"/>
+      <c r="AL2" s="343" t="n"/>
+      <c r="AM2" s="343" t="n"/>
+      <c r="AN2" s="343" t="n"/>
+      <c r="AO2" s="343" t="n"/>
+      <c r="AP2" s="344" t="n"/>
+      <c r="AQ2" s="345" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="282" t="n"/>
-      <c r="AS2" s="282" t="n"/>
-      <c r="AT2" s="282" t="n"/>
-      <c r="AU2" s="282" t="n"/>
-      <c r="AV2" s="283" t="n"/>
-      <c r="AW2" s="284" t="inlineStr">
+      <c r="AR2" s="346" t="n"/>
+      <c r="AS2" s="346" t="n"/>
+      <c r="AT2" s="346" t="n"/>
+      <c r="AU2" s="346" t="n"/>
+      <c r="AV2" s="347" t="n"/>
+      <c r="AW2" s="348" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="282" t="n"/>
-      <c r="AY2" s="282" t="n"/>
-      <c r="AZ2" s="282" t="n"/>
-      <c r="BA2" s="282" t="n"/>
-      <c r="BB2" s="282" t="n"/>
-      <c r="BC2" s="282" t="n"/>
-      <c r="BD2" s="285" t="n"/>
+      <c r="AX2" s="349" t="n"/>
+      <c r="AY2" s="349" t="n"/>
+      <c r="AZ2" s="349" t="n"/>
+      <c r="BA2" s="349" t="n"/>
+      <c r="BB2" s="349" t="n"/>
+      <c r="BC2" s="349" t="n"/>
+      <c r="BD2" s="350" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="281" t="inlineStr">
+      <c r="A3" s="351" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="352" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="352" t="n"/>
+      <c r="AQ3" s="353" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="282" t="n"/>
-      <c r="AS3" s="282" t="n"/>
-      <c r="AT3" s="282" t="n"/>
-      <c r="AU3" s="282" t="n"/>
-      <c r="AV3" s="283" t="n"/>
-      <c r="AW3" s="284" t="inlineStr">
+      <c r="AR3" s="354" t="n"/>
+      <c r="AS3" s="354" t="n"/>
+      <c r="AT3" s="354" t="n"/>
+      <c r="AU3" s="354" t="n"/>
+      <c r="AV3" s="355" t="n"/>
+      <c r="AW3" s="250" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="282" t="n"/>
-      <c r="AY3" s="282" t="n"/>
-      <c r="AZ3" s="282" t="n"/>
-      <c r="BA3" s="282" t="n"/>
-      <c r="BB3" s="282" t="n"/>
-      <c r="BC3" s="282" t="n"/>
-      <c r="BD3" s="285" t="n"/>
+      <c r="AX3" s="356" t="n"/>
+      <c r="AY3" s="356" t="n"/>
+      <c r="AZ3" s="356" t="n"/>
+      <c r="BA3" s="356" t="n"/>
+      <c r="BB3" s="356" t="n"/>
+      <c r="BC3" s="356" t="n"/>
+      <c r="BD3" s="357" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="202" t="inlineStr">
+      <c r="A4" s="351" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="352" t="n"/>
+      <c r="L4" s="358" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="281" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="352" t="n"/>
+      <c r="AQ4" s="353" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="282" t="n"/>
-      <c r="AS4" s="282" t="n"/>
-      <c r="AT4" s="282" t="n"/>
-      <c r="AU4" s="282" t="n"/>
-      <c r="AV4" s="283" t="n"/>
-      <c r="AW4" s="284" t="inlineStr">
+      <c r="AR4" s="354" t="n"/>
+      <c r="AS4" s="354" t="n"/>
+      <c r="AT4" s="354" t="n"/>
+      <c r="AU4" s="354" t="n"/>
+      <c r="AV4" s="355" t="n"/>
+      <c r="AW4" s="250" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="282" t="n"/>
-      <c r="AY4" s="282" t="n"/>
-      <c r="AZ4" s="282" t="n"/>
-      <c r="BA4" s="282" t="n"/>
-      <c r="BB4" s="282" t="n"/>
-      <c r="BC4" s="282" t="n"/>
-      <c r="BD4" s="285" t="n"/>
+      <c r="AX4" s="356" t="n"/>
+      <c r="AY4" s="356" t="n"/>
+      <c r="AZ4" s="356" t="n"/>
+      <c r="BA4" s="356" t="n"/>
+      <c r="BB4" s="356" t="n"/>
+      <c r="BC4" s="356" t="n"/>
+      <c r="BD4" s="357" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="351" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="352" t="n"/>
+      <c r="L5" s="359" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="286" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="352" t="n"/>
+      <c r="AQ5" s="353" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="287" t="n"/>
-      <c r="AS5" s="287" t="n"/>
-      <c r="AT5" s="287" t="n"/>
-      <c r="AU5" s="287" t="n"/>
-      <c r="AV5" s="288" t="n"/>
-      <c r="AW5" s="289" t="inlineStr">
+      <c r="AR5" s="354" t="n"/>
+      <c r="AS5" s="354" t="n"/>
+      <c r="AT5" s="354" t="n"/>
+      <c r="AU5" s="354" t="n"/>
+      <c r="AV5" s="355" t="n"/>
+      <c r="AW5" s="250" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="287" t="n"/>
-      <c r="AY5" s="287" t="n"/>
-      <c r="AZ5" s="287" t="n"/>
-      <c r="BA5" s="287" t="n"/>
-      <c r="BB5" s="287" t="n"/>
-      <c r="BC5" s="287" t="n"/>
-      <c r="BD5" s="290" t="n"/>
+      <c r="AX5" s="356" t="n"/>
+      <c r="AY5" s="356" t="n"/>
+      <c r="AZ5" s="356" t="n"/>
+      <c r="BA5" s="356" t="n"/>
+      <c r="BB5" s="356" t="n"/>
+      <c r="BC5" s="356" t="n"/>
+      <c r="BD5" s="357" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="211" t="n"/>
-      <c r="B6" s="211" t="n"/>
-      <c r="C6" s="211" t="n"/>
-      <c r="D6" s="211" t="n"/>
-      <c r="E6" s="211" t="n"/>
-      <c r="F6" s="211" t="n"/>
-      <c r="G6" s="211" t="n"/>
-      <c r="H6" s="211" t="n"/>
-      <c r="I6" s="211" t="n"/>
-      <c r="J6" s="211" t="n"/>
-      <c r="K6" s="211" t="n"/>
-      <c r="L6" s="211" t="n"/>
-      <c r="M6" s="211" t="n"/>
-      <c r="N6" s="211" t="n"/>
-      <c r="O6" s="211" t="n"/>
-      <c r="P6" s="211" t="n"/>
-      <c r="Q6" s="211" t="n"/>
-      <c r="R6" s="211" t="n"/>
-      <c r="S6" s="211" t="n"/>
-      <c r="T6" s="211" t="n"/>
-      <c r="U6" s="211" t="n"/>
-      <c r="V6" s="211" t="n"/>
-      <c r="W6" s="211" t="n"/>
-      <c r="X6" s="211" t="n"/>
-      <c r="Y6" s="211" t="n"/>
-      <c r="Z6" s="211" t="n"/>
-      <c r="AA6" s="211" t="n"/>
-      <c r="AB6" s="211" t="n"/>
-      <c r="AC6" s="211" t="n"/>
-      <c r="AD6" s="211" t="n"/>
-      <c r="AE6" s="211" t="n"/>
-      <c r="AF6" s="211" t="n"/>
-      <c r="AG6" s="211" t="n"/>
-      <c r="AH6" s="211" t="n"/>
-      <c r="AI6" s="211" t="n"/>
-      <c r="AJ6" s="211" t="n"/>
-      <c r="AK6" s="211" t="n"/>
-      <c r="AL6" s="211" t="n"/>
-      <c r="AM6" s="211" t="n"/>
-      <c r="AN6" s="211" t="n"/>
-      <c r="AO6" s="211" t="n"/>
-      <c r="AP6" s="211" t="n"/>
-      <c r="AQ6" s="211" t="n"/>
-      <c r="AR6" s="211" t="n"/>
-      <c r="AS6" s="211" t="n"/>
-      <c r="AT6" s="211" t="n"/>
-      <c r="AU6" s="211" t="n"/>
-      <c r="AV6" s="211" t="n"/>
-      <c r="AW6" s="211" t="n"/>
-      <c r="AX6" s="211" t="n"/>
-      <c r="AY6" s="211" t="n"/>
-      <c r="AZ6" s="211" t="n"/>
-      <c r="BA6" s="211" t="n"/>
-      <c r="BB6" s="211" t="n"/>
-      <c r="BC6" s="211" t="n"/>
-      <c r="BD6" s="211" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="360" t="n"/>
+      <c r="B6" s="361" t="n"/>
+      <c r="C6" s="361" t="n"/>
+      <c r="D6" s="361" t="n"/>
+      <c r="E6" s="361" t="n"/>
+      <c r="F6" s="361" t="n"/>
+      <c r="G6" s="361" t="n"/>
+      <c r="H6" s="361" t="n"/>
+      <c r="I6" s="361" t="n"/>
+      <c r="J6" s="361" t="n"/>
+      <c r="K6" s="362" t="n"/>
+      <c r="L6" s="361" t="n"/>
+      <c r="M6" s="361" t="n"/>
+      <c r="N6" s="361" t="n"/>
+      <c r="O6" s="361" t="n"/>
+      <c r="P6" s="361" t="n"/>
+      <c r="Q6" s="361" t="n"/>
+      <c r="R6" s="361" t="n"/>
+      <c r="S6" s="361" t="n"/>
+      <c r="T6" s="361" t="n"/>
+      <c r="U6" s="361" t="n"/>
+      <c r="V6" s="361" t="n"/>
+      <c r="W6" s="361" t="n"/>
+      <c r="X6" s="361" t="n"/>
+      <c r="Y6" s="361" t="n"/>
+      <c r="Z6" s="361" t="n"/>
+      <c r="AA6" s="361" t="n"/>
+      <c r="AB6" s="361" t="n"/>
+      <c r="AC6" s="361" t="n"/>
+      <c r="AD6" s="361" t="n"/>
+      <c r="AE6" s="361" t="n"/>
+      <c r="AF6" s="361" t="n"/>
+      <c r="AG6" s="361" t="n"/>
+      <c r="AH6" s="361" t="n"/>
+      <c r="AI6" s="361" t="n"/>
+      <c r="AJ6" s="361" t="n"/>
+      <c r="AK6" s="361" t="n"/>
+      <c r="AL6" s="361" t="n"/>
+      <c r="AM6" s="361" t="n"/>
+      <c r="AN6" s="361" t="n"/>
+      <c r="AO6" s="361" t="n"/>
+      <c r="AP6" s="362" t="n"/>
+      <c r="AQ6" s="363" t="n"/>
+      <c r="AR6" s="363" t="n"/>
+      <c r="AS6" s="363" t="n"/>
+      <c r="AT6" s="363" t="n"/>
+      <c r="AU6" s="363" t="n"/>
+      <c r="AV6" s="364" t="n"/>
+      <c r="AW6" s="365" t="n"/>
+      <c r="AX6" s="365" t="n"/>
+      <c r="AY6" s="365" t="n"/>
+      <c r="AZ6" s="365" t="n"/>
+      <c r="BA6" s="365" t="n"/>
+      <c r="BB6" s="365" t="n"/>
+      <c r="BC6" s="365" t="n"/>
+      <c r="BD6" s="366" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="367" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="292" t="inlineStr">
@@ -8015,67 +7706,67 @@
       <c r="BC21" s="248" t="n"/>
       <c r="BD21" s="248" t="n"/>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="291" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="267" t="inlineStr">
         <is>
           <t>NOTICE: Controlled support sheet. Keep one row per controlled reference item and maintain traceable owner, date and evidence linkage.</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
-      <c r="S22" s="6" t="n"/>
-      <c r="T22" s="6" t="n"/>
-      <c r="U22" s="6" t="n"/>
-      <c r="V22" s="6" t="n"/>
-      <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
-      <c r="AB22" s="6" t="n"/>
-      <c r="AC22" s="6" t="n"/>
-      <c r="AD22" s="6" t="n"/>
-      <c r="AE22" s="6" t="n"/>
-      <c r="AF22" s="6" t="n"/>
-      <c r="AG22" s="6" t="n"/>
-      <c r="AH22" s="6" t="n"/>
-      <c r="AI22" s="6" t="n"/>
-      <c r="AJ22" s="6" t="n"/>
-      <c r="AK22" s="6" t="n"/>
-      <c r="AL22" s="6" t="n"/>
-      <c r="AM22" s="6" t="n"/>
-      <c r="AN22" s="6" t="n"/>
-      <c r="AO22" s="6" t="n"/>
-      <c r="AP22" s="6" t="n"/>
-      <c r="AQ22" s="6" t="n"/>
-      <c r="AR22" s="6" t="n"/>
-      <c r="AS22" s="6" t="n"/>
-      <c r="AT22" s="6" t="n"/>
-      <c r="AU22" s="6" t="n"/>
-      <c r="AV22" s="6" t="n"/>
-      <c r="AW22" s="6" t="n"/>
-      <c r="AX22" s="6" t="n"/>
-      <c r="AY22" s="6" t="n"/>
-      <c r="AZ22" s="6" t="n"/>
-      <c r="BA22" s="6" t="n"/>
-      <c r="BB22" s="6" t="n"/>
-      <c r="BC22" s="6" t="n"/>
-      <c r="BD22" s="7" t="n"/>
+      <c r="B22" s="368" t="n"/>
+      <c r="C22" s="368" t="n"/>
+      <c r="D22" s="368" t="n"/>
+      <c r="E22" s="368" t="n"/>
+      <c r="F22" s="368" t="n"/>
+      <c r="G22" s="368" t="n"/>
+      <c r="H22" s="368" t="n"/>
+      <c r="I22" s="368" t="n"/>
+      <c r="J22" s="368" t="n"/>
+      <c r="K22" s="368" t="n"/>
+      <c r="L22" s="368" t="n"/>
+      <c r="M22" s="368" t="n"/>
+      <c r="N22" s="368" t="n"/>
+      <c r="O22" s="368" t="n"/>
+      <c r="P22" s="368" t="n"/>
+      <c r="Q22" s="368" t="n"/>
+      <c r="R22" s="368" t="n"/>
+      <c r="S22" s="368" t="n"/>
+      <c r="T22" s="368" t="n"/>
+      <c r="U22" s="368" t="n"/>
+      <c r="V22" s="368" t="n"/>
+      <c r="W22" s="368" t="n"/>
+      <c r="X22" s="368" t="n"/>
+      <c r="Y22" s="368" t="n"/>
+      <c r="Z22" s="368" t="n"/>
+      <c r="AA22" s="368" t="n"/>
+      <c r="AB22" s="368" t="n"/>
+      <c r="AC22" s="368" t="n"/>
+      <c r="AD22" s="368" t="n"/>
+      <c r="AE22" s="368" t="n"/>
+      <c r="AF22" s="368" t="n"/>
+      <c r="AG22" s="368" t="n"/>
+      <c r="AH22" s="368" t="n"/>
+      <c r="AI22" s="368" t="n"/>
+      <c r="AJ22" s="368" t="n"/>
+      <c r="AK22" s="368" t="n"/>
+      <c r="AL22" s="368" t="n"/>
+      <c r="AM22" s="368" t="n"/>
+      <c r="AN22" s="368" t="n"/>
+      <c r="AO22" s="368" t="n"/>
+      <c r="AP22" s="368" t="n"/>
+      <c r="AQ22" s="368" t="n"/>
+      <c r="AR22" s="368" t="n"/>
+      <c r="AS22" s="368" t="n"/>
+      <c r="AT22" s="368" t="n"/>
+      <c r="AU22" s="368" t="n"/>
+      <c r="AV22" s="368" t="n"/>
+      <c r="AW22" s="368" t="n"/>
+      <c r="AX22" s="368" t="n"/>
+      <c r="AY22" s="368" t="n"/>
+      <c r="AZ22" s="368" t="n"/>
+      <c r="BA22" s="368" t="n"/>
+      <c r="BB22" s="368" t="n"/>
+      <c r="BC22" s="368" t="n"/>
+      <c r="BD22" s="369" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1"/>
     <row r="24" ht="20" customHeight="1"/>
@@ -8398,7 +8089,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="277" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -8410,7 +8101,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="190" t="inlineStr">
+      <c r="L1" s="377" t="inlineStr">
         <is>
           <t>CERTIFICATION TRACKING LOG — EVIDENCE REFERENCE REGISTER</t>
         </is>
@@ -8444,7 +8135,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="278" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -8469,279 +8160,392 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="281" t="inlineStr">
+      <c r="A2" s="342" t="n"/>
+      <c r="B2" s="343" t="n"/>
+      <c r="C2" s="343" t="n"/>
+      <c r="D2" s="343" t="n"/>
+      <c r="E2" s="343" t="n"/>
+      <c r="F2" s="343" t="n"/>
+      <c r="G2" s="343" t="n"/>
+      <c r="H2" s="343" t="n"/>
+      <c r="I2" s="343" t="n"/>
+      <c r="J2" s="343" t="n"/>
+      <c r="K2" s="344" t="n"/>
+      <c r="L2" s="343" t="n"/>
+      <c r="M2" s="343" t="n"/>
+      <c r="N2" s="343" t="n"/>
+      <c r="O2" s="343" t="n"/>
+      <c r="P2" s="343" t="n"/>
+      <c r="Q2" s="343" t="n"/>
+      <c r="R2" s="343" t="n"/>
+      <c r="S2" s="343" t="n"/>
+      <c r="T2" s="343" t="n"/>
+      <c r="U2" s="343" t="n"/>
+      <c r="V2" s="343" t="n"/>
+      <c r="W2" s="343" t="n"/>
+      <c r="X2" s="343" t="n"/>
+      <c r="Y2" s="343" t="n"/>
+      <c r="Z2" s="343" t="n"/>
+      <c r="AA2" s="343" t="n"/>
+      <c r="AB2" s="343" t="n"/>
+      <c r="AC2" s="343" t="n"/>
+      <c r="AD2" s="343" t="n"/>
+      <c r="AE2" s="343" t="n"/>
+      <c r="AF2" s="343" t="n"/>
+      <c r="AG2" s="343" t="n"/>
+      <c r="AH2" s="343" t="n"/>
+      <c r="AI2" s="343" t="n"/>
+      <c r="AJ2" s="343" t="n"/>
+      <c r="AK2" s="343" t="n"/>
+      <c r="AL2" s="343" t="n"/>
+      <c r="AM2" s="343" t="n"/>
+      <c r="AN2" s="343" t="n"/>
+      <c r="AO2" s="343" t="n"/>
+      <c r="AP2" s="344" t="n"/>
+      <c r="AQ2" s="345" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="282" t="n"/>
-      <c r="AS2" s="282" t="n"/>
-      <c r="AT2" s="282" t="n"/>
-      <c r="AU2" s="282" t="n"/>
-      <c r="AV2" s="283" t="n"/>
-      <c r="AW2" s="284" t="inlineStr">
+      <c r="AR2" s="346" t="n"/>
+      <c r="AS2" s="346" t="n"/>
+      <c r="AT2" s="346" t="n"/>
+      <c r="AU2" s="346" t="n"/>
+      <c r="AV2" s="347" t="n"/>
+      <c r="AW2" s="348" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="282" t="n"/>
-      <c r="AY2" s="282" t="n"/>
-      <c r="AZ2" s="282" t="n"/>
-      <c r="BA2" s="282" t="n"/>
-      <c r="BB2" s="282" t="n"/>
-      <c r="BC2" s="282" t="n"/>
-      <c r="BD2" s="285" t="n"/>
+      <c r="AX2" s="349" t="n"/>
+      <c r="AY2" s="349" t="n"/>
+      <c r="AZ2" s="349" t="n"/>
+      <c r="BA2" s="349" t="n"/>
+      <c r="BB2" s="349" t="n"/>
+      <c r="BC2" s="349" t="n"/>
+      <c r="BD2" s="350" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="281" t="inlineStr">
+      <c r="A3" s="351" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="352" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="352" t="n"/>
+      <c r="AQ3" s="353" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="282" t="n"/>
-      <c r="AS3" s="282" t="n"/>
-      <c r="AT3" s="282" t="n"/>
-      <c r="AU3" s="282" t="n"/>
-      <c r="AV3" s="283" t="n"/>
-      <c r="AW3" s="284" t="inlineStr">
+      <c r="AR3" s="354" t="n"/>
+      <c r="AS3" s="354" t="n"/>
+      <c r="AT3" s="354" t="n"/>
+      <c r="AU3" s="354" t="n"/>
+      <c r="AV3" s="355" t="n"/>
+      <c r="AW3" s="250" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="282" t="n"/>
-      <c r="AY3" s="282" t="n"/>
-      <c r="AZ3" s="282" t="n"/>
-      <c r="BA3" s="282" t="n"/>
-      <c r="BB3" s="282" t="n"/>
-      <c r="BC3" s="282" t="n"/>
-      <c r="BD3" s="285" t="n"/>
+      <c r="AX3" s="356" t="n"/>
+      <c r="AY3" s="356" t="n"/>
+      <c r="AZ3" s="356" t="n"/>
+      <c r="BA3" s="356" t="n"/>
+      <c r="BB3" s="356" t="n"/>
+      <c r="BC3" s="356" t="n"/>
+      <c r="BD3" s="357" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="202" t="inlineStr">
+      <c r="A4" s="351" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="352" t="n"/>
+      <c r="L4" s="358" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="281" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="352" t="n"/>
+      <c r="AQ4" s="353" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="282" t="n"/>
-      <c r="AS4" s="282" t="n"/>
-      <c r="AT4" s="282" t="n"/>
-      <c r="AU4" s="282" t="n"/>
-      <c r="AV4" s="283" t="n"/>
-      <c r="AW4" s="284" t="inlineStr">
+      <c r="AR4" s="354" t="n"/>
+      <c r="AS4" s="354" t="n"/>
+      <c r="AT4" s="354" t="n"/>
+      <c r="AU4" s="354" t="n"/>
+      <c r="AV4" s="355" t="n"/>
+      <c r="AW4" s="250" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="282" t="n"/>
-      <c r="AY4" s="282" t="n"/>
-      <c r="AZ4" s="282" t="n"/>
-      <c r="BA4" s="282" t="n"/>
-      <c r="BB4" s="282" t="n"/>
-      <c r="BC4" s="282" t="n"/>
-      <c r="BD4" s="285" t="n"/>
+      <c r="AX4" s="356" t="n"/>
+      <c r="AY4" s="356" t="n"/>
+      <c r="AZ4" s="356" t="n"/>
+      <c r="BA4" s="356" t="n"/>
+      <c r="BB4" s="356" t="n"/>
+      <c r="BC4" s="356" t="n"/>
+      <c r="BD4" s="357" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="351" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="352" t="n"/>
+      <c r="L5" s="359" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="286" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="352" t="n"/>
+      <c r="AQ5" s="353" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="287" t="n"/>
-      <c r="AS5" s="287" t="n"/>
-      <c r="AT5" s="287" t="n"/>
-      <c r="AU5" s="287" t="n"/>
-      <c r="AV5" s="288" t="n"/>
-      <c r="AW5" s="289" t="inlineStr">
+      <c r="AR5" s="354" t="n"/>
+      <c r="AS5" s="354" t="n"/>
+      <c r="AT5" s="354" t="n"/>
+      <c r="AU5" s="354" t="n"/>
+      <c r="AV5" s="355" t="n"/>
+      <c r="AW5" s="250" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="287" t="n"/>
-      <c r="AY5" s="287" t="n"/>
-      <c r="AZ5" s="287" t="n"/>
-      <c r="BA5" s="287" t="n"/>
-      <c r="BB5" s="287" t="n"/>
-      <c r="BC5" s="287" t="n"/>
-      <c r="BD5" s="290" t="n"/>
+      <c r="AX5" s="356" t="n"/>
+      <c r="AY5" s="356" t="n"/>
+      <c r="AZ5" s="356" t="n"/>
+      <c r="BA5" s="356" t="n"/>
+      <c r="BB5" s="356" t="n"/>
+      <c r="BC5" s="356" t="n"/>
+      <c r="BD5" s="357" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="211" t="n"/>
-      <c r="B6" s="211" t="n"/>
-      <c r="C6" s="211" t="n"/>
-      <c r="D6" s="211" t="n"/>
-      <c r="E6" s="211" t="n"/>
-      <c r="F6" s="211" t="n"/>
-      <c r="G6" s="211" t="n"/>
-      <c r="H6" s="211" t="n"/>
-      <c r="I6" s="211" t="n"/>
-      <c r="J6" s="211" t="n"/>
-      <c r="K6" s="211" t="n"/>
-      <c r="L6" s="211" t="n"/>
-      <c r="M6" s="211" t="n"/>
-      <c r="N6" s="211" t="n"/>
-      <c r="O6" s="211" t="n"/>
-      <c r="P6" s="211" t="n"/>
-      <c r="Q6" s="211" t="n"/>
-      <c r="R6" s="211" t="n"/>
-      <c r="S6" s="211" t="n"/>
-      <c r="T6" s="211" t="n"/>
-      <c r="U6" s="211" t="n"/>
-      <c r="V6" s="211" t="n"/>
-      <c r="W6" s="211" t="n"/>
-      <c r="X6" s="211" t="n"/>
-      <c r="Y6" s="211" t="n"/>
-      <c r="Z6" s="211" t="n"/>
-      <c r="AA6" s="211" t="n"/>
-      <c r="AB6" s="211" t="n"/>
-      <c r="AC6" s="211" t="n"/>
-      <c r="AD6" s="211" t="n"/>
-      <c r="AE6" s="211" t="n"/>
-      <c r="AF6" s="211" t="n"/>
-      <c r="AG6" s="211" t="n"/>
-      <c r="AH6" s="211" t="n"/>
-      <c r="AI6" s="211" t="n"/>
-      <c r="AJ6" s="211" t="n"/>
-      <c r="AK6" s="211" t="n"/>
-      <c r="AL6" s="211" t="n"/>
-      <c r="AM6" s="211" t="n"/>
-      <c r="AN6" s="211" t="n"/>
-      <c r="AO6" s="211" t="n"/>
-      <c r="AP6" s="211" t="n"/>
-      <c r="AQ6" s="211" t="n"/>
-      <c r="AR6" s="211" t="n"/>
-      <c r="AS6" s="211" t="n"/>
-      <c r="AT6" s="211" t="n"/>
-      <c r="AU6" s="211" t="n"/>
-      <c r="AV6" s="211" t="n"/>
-      <c r="AW6" s="211" t="n"/>
-      <c r="AX6" s="211" t="n"/>
-      <c r="AY6" s="211" t="n"/>
-      <c r="AZ6" s="211" t="n"/>
-      <c r="BA6" s="211" t="n"/>
-      <c r="BB6" s="211" t="n"/>
-      <c r="BC6" s="211" t="n"/>
-      <c r="BD6" s="211" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="360" t="n"/>
+      <c r="B6" s="361" t="n"/>
+      <c r="C6" s="361" t="n"/>
+      <c r="D6" s="361" t="n"/>
+      <c r="E6" s="361" t="n"/>
+      <c r="F6" s="361" t="n"/>
+      <c r="G6" s="361" t="n"/>
+      <c r="H6" s="361" t="n"/>
+      <c r="I6" s="361" t="n"/>
+      <c r="J6" s="361" t="n"/>
+      <c r="K6" s="362" t="n"/>
+      <c r="L6" s="361" t="n"/>
+      <c r="M6" s="361" t="n"/>
+      <c r="N6" s="361" t="n"/>
+      <c r="O6" s="361" t="n"/>
+      <c r="P6" s="361" t="n"/>
+      <c r="Q6" s="361" t="n"/>
+      <c r="R6" s="361" t="n"/>
+      <c r="S6" s="361" t="n"/>
+      <c r="T6" s="361" t="n"/>
+      <c r="U6" s="361" t="n"/>
+      <c r="V6" s="361" t="n"/>
+      <c r="W6" s="361" t="n"/>
+      <c r="X6" s="361" t="n"/>
+      <c r="Y6" s="361" t="n"/>
+      <c r="Z6" s="361" t="n"/>
+      <c r="AA6" s="361" t="n"/>
+      <c r="AB6" s="361" t="n"/>
+      <c r="AC6" s="361" t="n"/>
+      <c r="AD6" s="361" t="n"/>
+      <c r="AE6" s="361" t="n"/>
+      <c r="AF6" s="361" t="n"/>
+      <c r="AG6" s="361" t="n"/>
+      <c r="AH6" s="361" t="n"/>
+      <c r="AI6" s="361" t="n"/>
+      <c r="AJ6" s="361" t="n"/>
+      <c r="AK6" s="361" t="n"/>
+      <c r="AL6" s="361" t="n"/>
+      <c r="AM6" s="361" t="n"/>
+      <c r="AN6" s="361" t="n"/>
+      <c r="AO6" s="361" t="n"/>
+      <c r="AP6" s="362" t="n"/>
+      <c r="AQ6" s="363" t="n"/>
+      <c r="AR6" s="363" t="n"/>
+      <c r="AS6" s="363" t="n"/>
+      <c r="AT6" s="363" t="n"/>
+      <c r="AU6" s="363" t="n"/>
+      <c r="AV6" s="364" t="n"/>
+      <c r="AW6" s="365" t="n"/>
+      <c r="AX6" s="365" t="n"/>
+      <c r="AY6" s="365" t="n"/>
+      <c r="AZ6" s="365" t="n"/>
+      <c r="BA6" s="365" t="n"/>
+      <c r="BB6" s="365" t="n"/>
+      <c r="BC6" s="365" t="n"/>
+      <c r="BD6" s="366" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="291" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  REFERENCE / SOURCE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="367" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="292" t="inlineStr">
@@ -9557,67 +9361,67 @@
       <c r="BC20" s="248" t="n"/>
       <c r="BD20" s="248" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="291" t="inlineStr">
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="267" t="inlineStr">
         <is>
           <t>NOTICE: Reference evidence by owner, date and source path only; do not duplicate system-owned master records in this support sheet.</t>
         </is>
       </c>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
-      <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n"/>
-      <c r="N21" s="6" t="n"/>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n"/>
-      <c r="Q21" s="6" t="n"/>
-      <c r="R21" s="6" t="n"/>
-      <c r="S21" s="6" t="n"/>
-      <c r="T21" s="6" t="n"/>
-      <c r="U21" s="6" t="n"/>
-      <c r="V21" s="6" t="n"/>
-      <c r="W21" s="6" t="n"/>
-      <c r="X21" s="6" t="n"/>
-      <c r="Y21" s="6" t="n"/>
-      <c r="Z21" s="6" t="n"/>
-      <c r="AA21" s="6" t="n"/>
-      <c r="AB21" s="6" t="n"/>
-      <c r="AC21" s="6" t="n"/>
-      <c r="AD21" s="6" t="n"/>
-      <c r="AE21" s="6" t="n"/>
-      <c r="AF21" s="6" t="n"/>
-      <c r="AG21" s="6" t="n"/>
-      <c r="AH21" s="6" t="n"/>
-      <c r="AI21" s="6" t="n"/>
-      <c r="AJ21" s="6" t="n"/>
-      <c r="AK21" s="6" t="n"/>
-      <c r="AL21" s="6" t="n"/>
-      <c r="AM21" s="6" t="n"/>
-      <c r="AN21" s="6" t="n"/>
-      <c r="AO21" s="6" t="n"/>
-      <c r="AP21" s="6" t="n"/>
-      <c r="AQ21" s="6" t="n"/>
-      <c r="AR21" s="6" t="n"/>
-      <c r="AS21" s="6" t="n"/>
-      <c r="AT21" s="6" t="n"/>
-      <c r="AU21" s="6" t="n"/>
-      <c r="AV21" s="6" t="n"/>
-      <c r="AW21" s="6" t="n"/>
-      <c r="AX21" s="6" t="n"/>
-      <c r="AY21" s="6" t="n"/>
-      <c r="AZ21" s="6" t="n"/>
-      <c r="BA21" s="6" t="n"/>
-      <c r="BB21" s="6" t="n"/>
-      <c r="BC21" s="6" t="n"/>
-      <c r="BD21" s="7" t="n"/>
+      <c r="B21" s="368" t="n"/>
+      <c r="C21" s="368" t="n"/>
+      <c r="D21" s="368" t="n"/>
+      <c r="E21" s="368" t="n"/>
+      <c r="F21" s="368" t="n"/>
+      <c r="G21" s="368" t="n"/>
+      <c r="H21" s="368" t="n"/>
+      <c r="I21" s="368" t="n"/>
+      <c r="J21" s="368" t="n"/>
+      <c r="K21" s="368" t="n"/>
+      <c r="L21" s="368" t="n"/>
+      <c r="M21" s="368" t="n"/>
+      <c r="N21" s="368" t="n"/>
+      <c r="O21" s="368" t="n"/>
+      <c r="P21" s="368" t="n"/>
+      <c r="Q21" s="368" t="n"/>
+      <c r="R21" s="368" t="n"/>
+      <c r="S21" s="368" t="n"/>
+      <c r="T21" s="368" t="n"/>
+      <c r="U21" s="368" t="n"/>
+      <c r="V21" s="368" t="n"/>
+      <c r="W21" s="368" t="n"/>
+      <c r="X21" s="368" t="n"/>
+      <c r="Y21" s="368" t="n"/>
+      <c r="Z21" s="368" t="n"/>
+      <c r="AA21" s="368" t="n"/>
+      <c r="AB21" s="368" t="n"/>
+      <c r="AC21" s="368" t="n"/>
+      <c r="AD21" s="368" t="n"/>
+      <c r="AE21" s="368" t="n"/>
+      <c r="AF21" s="368" t="n"/>
+      <c r="AG21" s="368" t="n"/>
+      <c r="AH21" s="368" t="n"/>
+      <c r="AI21" s="368" t="n"/>
+      <c r="AJ21" s="368" t="n"/>
+      <c r="AK21" s="368" t="n"/>
+      <c r="AL21" s="368" t="n"/>
+      <c r="AM21" s="368" t="n"/>
+      <c r="AN21" s="368" t="n"/>
+      <c r="AO21" s="368" t="n"/>
+      <c r="AP21" s="368" t="n"/>
+      <c r="AQ21" s="368" t="n"/>
+      <c r="AR21" s="368" t="n"/>
+      <c r="AS21" s="368" t="n"/>
+      <c r="AT21" s="368" t="n"/>
+      <c r="AU21" s="368" t="n"/>
+      <c r="AV21" s="368" t="n"/>
+      <c r="AW21" s="368" t="n"/>
+      <c r="AX21" s="368" t="n"/>
+      <c r="AY21" s="368" t="n"/>
+      <c r="AZ21" s="368" t="n"/>
+      <c r="BA21" s="368" t="n"/>
+      <c r="BB21" s="368" t="n"/>
+      <c r="BC21" s="368" t="n"/>
+      <c r="BD21" s="369" t="n"/>
     </row>
     <row r="22" ht="20" customHeight="1"/>
     <row r="23" ht="20" customHeight="1"/>
@@ -9969,7 +9773,7 @@
     <col width="2.33" customWidth="1" min="56" max="56"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="277" t="n"/>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="2" t="n"/>
@@ -9981,7 +9785,7 @@
       <c r="I1" s="2" t="n"/>
       <c r="J1" s="2" t="n"/>
       <c r="K1" s="3" t="n"/>
-      <c r="L1" s="259" t="inlineStr">
+      <c r="L1" s="378" t="inlineStr">
         <is>
           <t>CERTIFICATION TRACKING LOG — CONTROLLED LOOKUP LISTS</t>
         </is>
@@ -10015,7 +9819,7 @@
       <c r="AM1" s="2" t="n"/>
       <c r="AN1" s="2" t="n"/>
       <c r="AO1" s="2" t="n"/>
-      <c r="AP1" s="2" t="n"/>
+      <c r="AP1" s="3" t="n"/>
       <c r="AQ1" s="333" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -10040,286 +9844,454 @@
       <c r="BD1" s="3" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="9" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="9" t="n"/>
-      <c r="AQ2" s="335" t="inlineStr">
+      <c r="A2" s="342" t="n"/>
+      <c r="B2" s="343" t="n"/>
+      <c r="C2" s="343" t="n"/>
+      <c r="D2" s="343" t="n"/>
+      <c r="E2" s="343" t="n"/>
+      <c r="F2" s="343" t="n"/>
+      <c r="G2" s="343" t="n"/>
+      <c r="H2" s="343" t="n"/>
+      <c r="I2" s="343" t="n"/>
+      <c r="J2" s="343" t="n"/>
+      <c r="K2" s="344" t="n"/>
+      <c r="L2" s="343" t="n"/>
+      <c r="M2" s="343" t="n"/>
+      <c r="N2" s="343" t="n"/>
+      <c r="O2" s="343" t="n"/>
+      <c r="P2" s="343" t="n"/>
+      <c r="Q2" s="343" t="n"/>
+      <c r="R2" s="343" t="n"/>
+      <c r="S2" s="343" t="n"/>
+      <c r="T2" s="343" t="n"/>
+      <c r="U2" s="343" t="n"/>
+      <c r="V2" s="343" t="n"/>
+      <c r="W2" s="343" t="n"/>
+      <c r="X2" s="343" t="n"/>
+      <c r="Y2" s="343" t="n"/>
+      <c r="Z2" s="343" t="n"/>
+      <c r="AA2" s="343" t="n"/>
+      <c r="AB2" s="343" t="n"/>
+      <c r="AC2" s="343" t="n"/>
+      <c r="AD2" s="343" t="n"/>
+      <c r="AE2" s="343" t="n"/>
+      <c r="AF2" s="343" t="n"/>
+      <c r="AG2" s="343" t="n"/>
+      <c r="AH2" s="343" t="n"/>
+      <c r="AI2" s="343" t="n"/>
+      <c r="AJ2" s="343" t="n"/>
+      <c r="AK2" s="343" t="n"/>
+      <c r="AL2" s="343" t="n"/>
+      <c r="AM2" s="343" t="n"/>
+      <c r="AN2" s="343" t="n"/>
+      <c r="AO2" s="343" t="n"/>
+      <c r="AP2" s="344" t="n"/>
+      <c r="AQ2" s="345" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="282" t="n"/>
-      <c r="AS2" s="282" t="n"/>
-      <c r="AT2" s="282" t="n"/>
-      <c r="AU2" s="282" t="n"/>
-      <c r="AV2" s="283" t="n"/>
-      <c r="AW2" s="336" t="inlineStr">
+      <c r="AR2" s="346" t="n"/>
+      <c r="AS2" s="346" t="n"/>
+      <c r="AT2" s="346" t="n"/>
+      <c r="AU2" s="346" t="n"/>
+      <c r="AV2" s="347" t="n"/>
+      <c r="AW2" s="348" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="282" t="n"/>
-      <c r="AY2" s="282" t="n"/>
-      <c r="AZ2" s="282" t="n"/>
-      <c r="BA2" s="282" t="n"/>
-      <c r="BB2" s="282" t="n"/>
-      <c r="BC2" s="282" t="n"/>
-      <c r="BD2" s="285" t="n"/>
+      <c r="AX2" s="349" t="n"/>
+      <c r="AY2" s="349" t="n"/>
+      <c r="AZ2" s="349" t="n"/>
+      <c r="BA2" s="349" t="n"/>
+      <c r="BB2" s="349" t="n"/>
+      <c r="BC2" s="349" t="n"/>
+      <c r="BD2" s="350" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="9" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="9" t="n"/>
-      <c r="AQ3" s="335" t="inlineStr">
+      <c r="A3" s="351" t="n"/>
+      <c r="B3" s="46" t="n"/>
+      <c r="C3" s="46" t="n"/>
+      <c r="D3" s="46" t="n"/>
+      <c r="E3" s="46" t="n"/>
+      <c r="F3" s="46" t="n"/>
+      <c r="G3" s="46" t="n"/>
+      <c r="H3" s="46" t="n"/>
+      <c r="I3" s="46" t="n"/>
+      <c r="J3" s="46" t="n"/>
+      <c r="K3" s="352" t="n"/>
+      <c r="L3" s="46" t="n"/>
+      <c r="M3" s="46" t="n"/>
+      <c r="N3" s="46" t="n"/>
+      <c r="O3" s="46" t="n"/>
+      <c r="P3" s="46" t="n"/>
+      <c r="Q3" s="46" t="n"/>
+      <c r="R3" s="46" t="n"/>
+      <c r="S3" s="46" t="n"/>
+      <c r="T3" s="46" t="n"/>
+      <c r="U3" s="46" t="n"/>
+      <c r="V3" s="46" t="n"/>
+      <c r="W3" s="46" t="n"/>
+      <c r="X3" s="46" t="n"/>
+      <c r="Y3" s="46" t="n"/>
+      <c r="Z3" s="46" t="n"/>
+      <c r="AA3" s="46" t="n"/>
+      <c r="AB3" s="46" t="n"/>
+      <c r="AC3" s="46" t="n"/>
+      <c r="AD3" s="46" t="n"/>
+      <c r="AE3" s="46" t="n"/>
+      <c r="AF3" s="46" t="n"/>
+      <c r="AG3" s="46" t="n"/>
+      <c r="AH3" s="46" t="n"/>
+      <c r="AI3" s="46" t="n"/>
+      <c r="AJ3" s="46" t="n"/>
+      <c r="AK3" s="46" t="n"/>
+      <c r="AL3" s="46" t="n"/>
+      <c r="AM3" s="46" t="n"/>
+      <c r="AN3" s="46" t="n"/>
+      <c r="AO3" s="46" t="n"/>
+      <c r="AP3" s="352" t="n"/>
+      <c r="AQ3" s="353" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="282" t="n"/>
-      <c r="AS3" s="282" t="n"/>
-      <c r="AT3" s="282" t="n"/>
-      <c r="AU3" s="282" t="n"/>
-      <c r="AV3" s="283" t="n"/>
-      <c r="AW3" s="336" t="inlineStr">
+      <c r="AR3" s="354" t="n"/>
+      <c r="AS3" s="354" t="n"/>
+      <c r="AT3" s="354" t="n"/>
+      <c r="AU3" s="354" t="n"/>
+      <c r="AV3" s="355" t="n"/>
+      <c r="AW3" s="250" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="282" t="n"/>
-      <c r="AY3" s="282" t="n"/>
-      <c r="AZ3" s="282" t="n"/>
-      <c r="BA3" s="282" t="n"/>
-      <c r="BB3" s="282" t="n"/>
-      <c r="BC3" s="282" t="n"/>
-      <c r="BD3" s="285" t="n"/>
+      <c r="AX3" s="356" t="n"/>
+      <c r="AY3" s="356" t="n"/>
+      <c r="AZ3" s="356" t="n"/>
+      <c r="BA3" s="356" t="n"/>
+      <c r="BB3" s="356" t="n"/>
+      <c r="BC3" s="356" t="n"/>
+      <c r="BD3" s="357" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="9" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="41" t="inlineStr">
+      <c r="A4" s="351" t="n"/>
+      <c r="B4" s="46" t="n"/>
+      <c r="C4" s="46" t="n"/>
+      <c r="D4" s="46" t="n"/>
+      <c r="E4" s="46" t="n"/>
+      <c r="F4" s="46" t="n"/>
+      <c r="G4" s="46" t="n"/>
+      <c r="H4" s="46" t="n"/>
+      <c r="I4" s="46" t="n"/>
+      <c r="J4" s="46" t="n"/>
+      <c r="K4" s="352" t="n"/>
+      <c r="L4" s="358" t="inlineStr">
         <is>
           <t>Quality Management System · Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="335" t="inlineStr">
+      <c r="M4" s="46" t="n"/>
+      <c r="N4" s="46" t="n"/>
+      <c r="O4" s="46" t="n"/>
+      <c r="P4" s="46" t="n"/>
+      <c r="Q4" s="46" t="n"/>
+      <c r="R4" s="46" t="n"/>
+      <c r="S4" s="46" t="n"/>
+      <c r="T4" s="46" t="n"/>
+      <c r="U4" s="46" t="n"/>
+      <c r="V4" s="46" t="n"/>
+      <c r="W4" s="46" t="n"/>
+      <c r="X4" s="46" t="n"/>
+      <c r="Y4" s="46" t="n"/>
+      <c r="Z4" s="46" t="n"/>
+      <c r="AA4" s="46" t="n"/>
+      <c r="AB4" s="46" t="n"/>
+      <c r="AC4" s="46" t="n"/>
+      <c r="AD4" s="46" t="n"/>
+      <c r="AE4" s="46" t="n"/>
+      <c r="AF4" s="46" t="n"/>
+      <c r="AG4" s="46" t="n"/>
+      <c r="AH4" s="46" t="n"/>
+      <c r="AI4" s="46" t="n"/>
+      <c r="AJ4" s="46" t="n"/>
+      <c r="AK4" s="46" t="n"/>
+      <c r="AL4" s="46" t="n"/>
+      <c r="AM4" s="46" t="n"/>
+      <c r="AN4" s="46" t="n"/>
+      <c r="AO4" s="46" t="n"/>
+      <c r="AP4" s="352" t="n"/>
+      <c r="AQ4" s="353" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="282" t="n"/>
-      <c r="AS4" s="282" t="n"/>
-      <c r="AT4" s="282" t="n"/>
-      <c r="AU4" s="282" t="n"/>
-      <c r="AV4" s="283" t="n"/>
-      <c r="AW4" s="336" t="inlineStr">
+      <c r="AR4" s="354" t="n"/>
+      <c r="AS4" s="354" t="n"/>
+      <c r="AT4" s="354" t="n"/>
+      <c r="AU4" s="354" t="n"/>
+      <c r="AV4" s="355" t="n"/>
+      <c r="AW4" s="250" t="inlineStr">
         <is>
           <t>HR + Department Manager</t>
         </is>
       </c>
-      <c r="AX4" s="282" t="n"/>
-      <c r="AY4" s="282" t="n"/>
-      <c r="AZ4" s="282" t="n"/>
-      <c r="BA4" s="282" t="n"/>
-      <c r="BB4" s="282" t="n"/>
-      <c r="BC4" s="282" t="n"/>
-      <c r="BD4" s="285" t="n"/>
+      <c r="AX4" s="356" t="n"/>
+      <c r="AY4" s="356" t="n"/>
+      <c r="AZ4" s="356" t="n"/>
+      <c r="BA4" s="356" t="n"/>
+      <c r="BB4" s="356" t="n"/>
+      <c r="BC4" s="356" t="n"/>
+      <c r="BD4" s="357" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="n"/>
-      <c r="C5" s="13" t="n"/>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="13" t="n"/>
-      <c r="G5" s="13" t="n"/>
-      <c r="H5" s="13" t="n"/>
-      <c r="I5" s="13" t="n"/>
-      <c r="J5" s="13" t="n"/>
-      <c r="K5" s="14" t="n"/>
-      <c r="L5" s="42" t="inlineStr">
+      <c r="A5" s="351" t="n"/>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="46" t="n"/>
+      <c r="I5" s="46" t="n"/>
+      <c r="J5" s="46" t="n"/>
+      <c r="K5" s="352" t="n"/>
+      <c r="L5" s="359" t="inlineStr">
         <is>
           <t>HESEM Engineering · ISO 9001 / AS9100 · Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="13" t="n"/>
-      <c r="N5" s="13" t="n"/>
-      <c r="O5" s="13" t="n"/>
-      <c r="P5" s="13" t="n"/>
-      <c r="Q5" s="13" t="n"/>
-      <c r="R5" s="13" t="n"/>
-      <c r="S5" s="13" t="n"/>
-      <c r="T5" s="13" t="n"/>
-      <c r="U5" s="13" t="n"/>
-      <c r="V5" s="13" t="n"/>
-      <c r="W5" s="13" t="n"/>
-      <c r="X5" s="13" t="n"/>
-      <c r="Y5" s="13" t="n"/>
-      <c r="Z5" s="13" t="n"/>
-      <c r="AA5" s="13" t="n"/>
-      <c r="AB5" s="13" t="n"/>
-      <c r="AC5" s="13" t="n"/>
-      <c r="AD5" s="13" t="n"/>
-      <c r="AE5" s="13" t="n"/>
-      <c r="AF5" s="13" t="n"/>
-      <c r="AG5" s="13" t="n"/>
-      <c r="AH5" s="13" t="n"/>
-      <c r="AI5" s="13" t="n"/>
-      <c r="AJ5" s="13" t="n"/>
-      <c r="AK5" s="13" t="n"/>
-      <c r="AL5" s="13" t="n"/>
-      <c r="AM5" s="13" t="n"/>
-      <c r="AN5" s="13" t="n"/>
-      <c r="AO5" s="13" t="n"/>
-      <c r="AP5" s="13" t="n"/>
-      <c r="AQ5" s="337" t="inlineStr">
+      <c r="M5" s="46" t="n"/>
+      <c r="N5" s="46" t="n"/>
+      <c r="O5" s="46" t="n"/>
+      <c r="P5" s="46" t="n"/>
+      <c r="Q5" s="46" t="n"/>
+      <c r="R5" s="46" t="n"/>
+      <c r="S5" s="46" t="n"/>
+      <c r="T5" s="46" t="n"/>
+      <c r="U5" s="46" t="n"/>
+      <c r="V5" s="46" t="n"/>
+      <c r="W5" s="46" t="n"/>
+      <c r="X5" s="46" t="n"/>
+      <c r="Y5" s="46" t="n"/>
+      <c r="Z5" s="46" t="n"/>
+      <c r="AA5" s="46" t="n"/>
+      <c r="AB5" s="46" t="n"/>
+      <c r="AC5" s="46" t="n"/>
+      <c r="AD5" s="46" t="n"/>
+      <c r="AE5" s="46" t="n"/>
+      <c r="AF5" s="46" t="n"/>
+      <c r="AG5" s="46" t="n"/>
+      <c r="AH5" s="46" t="n"/>
+      <c r="AI5" s="46" t="n"/>
+      <c r="AJ5" s="46" t="n"/>
+      <c r="AK5" s="46" t="n"/>
+      <c r="AL5" s="46" t="n"/>
+      <c r="AM5" s="46" t="n"/>
+      <c r="AN5" s="46" t="n"/>
+      <c r="AO5" s="46" t="n"/>
+      <c r="AP5" s="352" t="n"/>
+      <c r="AQ5" s="353" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="287" t="n"/>
-      <c r="AS5" s="287" t="n"/>
-      <c r="AT5" s="287" t="n"/>
-      <c r="AU5" s="287" t="n"/>
-      <c r="AV5" s="288" t="n"/>
-      <c r="AW5" s="338" t="inlineStr">
+      <c r="AR5" s="354" t="n"/>
+      <c r="AS5" s="354" t="n"/>
+      <c r="AT5" s="354" t="n"/>
+      <c r="AU5" s="354" t="n"/>
+      <c r="AV5" s="355" t="n"/>
+      <c r="AW5" s="250" t="inlineStr">
         <is>
           <t>Per authority matrix</t>
         </is>
       </c>
-      <c r="AX5" s="287" t="n"/>
-      <c r="AY5" s="287" t="n"/>
-      <c r="AZ5" s="287" t="n"/>
-      <c r="BA5" s="287" t="n"/>
-      <c r="BB5" s="287" t="n"/>
-      <c r="BC5" s="287" t="n"/>
-      <c r="BD5" s="290" t="n"/>
+      <c r="AX5" s="356" t="n"/>
+      <c r="AY5" s="356" t="n"/>
+      <c r="AZ5" s="356" t="n"/>
+      <c r="BA5" s="356" t="n"/>
+      <c r="BB5" s="356" t="n"/>
+      <c r="BC5" s="356" t="n"/>
+      <c r="BD5" s="357" t="n"/>
     </row>
-    <row r="6" ht="4" customHeight="1">
-      <c r="A6" s="248" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="360" t="n"/>
+      <c r="B6" s="370" t="n"/>
+      <c r="C6" s="370" t="n"/>
+      <c r="D6" s="370" t="n"/>
+      <c r="E6" s="370" t="n"/>
+      <c r="F6" s="370" t="n"/>
+      <c r="G6" s="370" t="n"/>
+      <c r="H6" s="370" t="n"/>
+      <c r="I6" s="370" t="n"/>
+      <c r="J6" s="370" t="n"/>
+      <c r="K6" s="371" t="n"/>
+      <c r="L6" s="370" t="n"/>
+      <c r="M6" s="370" t="n"/>
+      <c r="N6" s="370" t="n"/>
+      <c r="O6" s="370" t="n"/>
+      <c r="P6" s="370" t="n"/>
+      <c r="Q6" s="370" t="n"/>
+      <c r="R6" s="370" t="n"/>
+      <c r="S6" s="370" t="n"/>
+      <c r="T6" s="370" t="n"/>
+      <c r="U6" s="370" t="n"/>
+      <c r="V6" s="370" t="n"/>
+      <c r="W6" s="370" t="n"/>
+      <c r="X6" s="370" t="n"/>
+      <c r="Y6" s="370" t="n"/>
+      <c r="Z6" s="370" t="n"/>
+      <c r="AA6" s="370" t="n"/>
+      <c r="AB6" s="370" t="n"/>
+      <c r="AC6" s="370" t="n"/>
+      <c r="AD6" s="370" t="n"/>
+      <c r="AE6" s="370" t="n"/>
+      <c r="AF6" s="370" t="n"/>
+      <c r="AG6" s="370" t="n"/>
+      <c r="AH6" s="370" t="n"/>
+      <c r="AI6" s="370" t="n"/>
+      <c r="AJ6" s="370" t="n"/>
+      <c r="AK6" s="370" t="n"/>
+      <c r="AL6" s="370" t="n"/>
+      <c r="AM6" s="370" t="n"/>
+      <c r="AN6" s="370" t="n"/>
+      <c r="AO6" s="370" t="n"/>
+      <c r="AP6" s="371" t="n"/>
+      <c r="AQ6" s="372" t="n"/>
+      <c r="AR6" s="372" t="n"/>
+      <c r="AS6" s="372" t="n"/>
+      <c r="AT6" s="372" t="n"/>
+      <c r="AU6" s="372" t="n"/>
+      <c r="AV6" s="373" t="n"/>
+      <c r="AW6" s="374" t="n"/>
+      <c r="AX6" s="374" t="n"/>
+      <c r="AY6" s="374" t="n"/>
+      <c r="AZ6" s="374" t="n"/>
+      <c r="BA6" s="374" t="n"/>
+      <c r="BB6" s="374" t="n"/>
+      <c r="BC6" s="374" t="n"/>
+      <c r="BD6" s="375" t="n"/>
     </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  1. CONTROLLED LOOKUP LISTS</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="n"/>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-      <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
-      <c r="L7" s="6" t="n"/>
-      <c r="M7" s="6" t="n"/>
-      <c r="N7" s="6" t="n"/>
-      <c r="O7" s="6" t="n"/>
-      <c r="P7" s="6" t="n"/>
-      <c r="Q7" s="6" t="n"/>
-      <c r="R7" s="6" t="n"/>
-      <c r="S7" s="6" t="n"/>
-      <c r="T7" s="6" t="n"/>
-      <c r="U7" s="6" t="n"/>
-      <c r="V7" s="6" t="n"/>
-      <c r="W7" s="6" t="n"/>
-      <c r="X7" s="6" t="n"/>
-      <c r="Y7" s="6" t="n"/>
-      <c r="Z7" s="6" t="n"/>
-      <c r="AA7" s="6" t="n"/>
-      <c r="AB7" s="6" t="n"/>
-      <c r="AC7" s="6" t="n"/>
-      <c r="AD7" s="6" t="n"/>
-      <c r="AE7" s="6" t="n"/>
-      <c r="AF7" s="6" t="n"/>
-      <c r="AG7" s="6" t="n"/>
-      <c r="AH7" s="6" t="n"/>
-      <c r="AI7" s="6" t="n"/>
-      <c r="AJ7" s="6" t="n"/>
-      <c r="AK7" s="6" t="n"/>
-      <c r="AL7" s="6" t="n"/>
-      <c r="AM7" s="6" t="n"/>
-      <c r="AN7" s="6" t="n"/>
-      <c r="AO7" s="6" t="n"/>
-      <c r="AP7" s="6" t="n"/>
-      <c r="AQ7" s="6" t="n"/>
-      <c r="AR7" s="6" t="n"/>
-      <c r="AS7" s="6" t="n"/>
-      <c r="AT7" s="6" t="n"/>
-      <c r="AU7" s="6" t="n"/>
-      <c r="AV7" s="6" t="n"/>
-      <c r="AW7" s="6" t="n"/>
-      <c r="AX7" s="6" t="n"/>
-      <c r="AY7" s="6" t="n"/>
-      <c r="AZ7" s="6" t="n"/>
-      <c r="BA7" s="6" t="n"/>
-      <c r="BB7" s="6" t="n"/>
-      <c r="BC7" s="6" t="n"/>
-      <c r="BD7" s="7" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="376" t="n"/>
+      <c r="B7" s="17" t="n"/>
+      <c r="C7" s="17" t="n"/>
+      <c r="D7" s="17" t="n"/>
+      <c r="E7" s="17" t="n"/>
+      <c r="F7" s="17" t="n"/>
+      <c r="G7" s="17" t="n"/>
+      <c r="H7" s="17" t="n"/>
+      <c r="I7" s="17" t="n"/>
+      <c r="J7" s="17" t="n"/>
+      <c r="K7" s="17" t="n"/>
+      <c r="L7" s="17" t="n"/>
+      <c r="M7" s="17" t="n"/>
+      <c r="N7" s="17" t="n"/>
+      <c r="O7" s="17" t="n"/>
+      <c r="P7" s="17" t="n"/>
+      <c r="Q7" s="17" t="n"/>
+      <c r="R7" s="17" t="n"/>
+      <c r="S7" s="17" t="n"/>
+      <c r="T7" s="17" t="n"/>
+      <c r="U7" s="17" t="n"/>
+      <c r="V7" s="17" t="n"/>
+      <c r="W7" s="17" t="n"/>
+      <c r="X7" s="17" t="n"/>
+      <c r="Y7" s="17" t="n"/>
+      <c r="Z7" s="17" t="n"/>
+      <c r="AA7" s="17" t="n"/>
+      <c r="AB7" s="17" t="n"/>
+      <c r="AC7" s="17" t="n"/>
+      <c r="AD7" s="17" t="n"/>
+      <c r="AE7" s="17" t="n"/>
+      <c r="AF7" s="17" t="n"/>
+      <c r="AG7" s="17" t="n"/>
+      <c r="AH7" s="17" t="n"/>
+      <c r="AI7" s="17" t="n"/>
+      <c r="AJ7" s="17" t="n"/>
+      <c r="AK7" s="17" t="n"/>
+      <c r="AL7" s="17" t="n"/>
+      <c r="AM7" s="17" t="n"/>
+      <c r="AN7" s="17" t="n"/>
+      <c r="AO7" s="17" t="n"/>
+      <c r="AP7" s="17" t="n"/>
+      <c r="AQ7" s="17" t="n"/>
+      <c r="AR7" s="17" t="n"/>
+      <c r="AS7" s="17" t="n"/>
+      <c r="AT7" s="17" t="n"/>
+      <c r="AU7" s="17" t="n"/>
+      <c r="AV7" s="17" t="n"/>
+      <c r="AW7" s="17" t="n"/>
+      <c r="AX7" s="17" t="n"/>
+      <c r="AY7" s="17" t="n"/>
+      <c r="AZ7" s="17" t="n"/>
+      <c r="BA7" s="17" t="n"/>
+      <c r="BB7" s="17" t="n"/>
+      <c r="BC7" s="17" t="n"/>
+      <c r="BD7" s="17" t="n"/>
     </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="25" t="inlineStr">
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="267" t="inlineStr">
         <is>
           <t>NOTICE: Controlled dropdown source sheet. Do not edit values without formal document control because validations in the workbook depend on these lists.</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-      <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
-      <c r="L8" s="6" t="n"/>
-      <c r="M8" s="6" t="n"/>
-      <c r="N8" s="6" t="n"/>
-      <c r="O8" s="6" t="n"/>
-      <c r="P8" s="6" t="n"/>
-      <c r="Q8" s="6" t="n"/>
-      <c r="R8" s="6" t="n"/>
-      <c r="S8" s="6" t="n"/>
-      <c r="T8" s="6" t="n"/>
-      <c r="U8" s="6" t="n"/>
-      <c r="V8" s="6" t="n"/>
-      <c r="W8" s="6" t="n"/>
-      <c r="X8" s="6" t="n"/>
-      <c r="Y8" s="6" t="n"/>
-      <c r="Z8" s="6" t="n"/>
-      <c r="AA8" s="6" t="n"/>
-      <c r="AB8" s="6" t="n"/>
-      <c r="AC8" s="6" t="n"/>
-      <c r="AD8" s="6" t="n"/>
-      <c r="AE8" s="6" t="n"/>
-      <c r="AF8" s="6" t="n"/>
-      <c r="AG8" s="6" t="n"/>
-      <c r="AH8" s="6" t="n"/>
-      <c r="AI8" s="6" t="n"/>
-      <c r="AJ8" s="6" t="n"/>
-      <c r="AK8" s="6" t="n"/>
-      <c r="AL8" s="6" t="n"/>
-      <c r="AM8" s="6" t="n"/>
-      <c r="AN8" s="6" t="n"/>
-      <c r="AO8" s="6" t="n"/>
-      <c r="AP8" s="6" t="n"/>
-      <c r="AQ8" s="6" t="n"/>
-      <c r="AR8" s="6" t="n"/>
-      <c r="AS8" s="6" t="n"/>
-      <c r="AT8" s="6" t="n"/>
-      <c r="AU8" s="6" t="n"/>
-      <c r="AV8" s="6" t="n"/>
-      <c r="AW8" s="6" t="n"/>
-      <c r="AX8" s="6" t="n"/>
-      <c r="AY8" s="6" t="n"/>
-      <c r="AZ8" s="6" t="n"/>
-      <c r="BA8" s="6" t="n"/>
-      <c r="BB8" s="6" t="n"/>
-      <c r="BC8" s="6" t="n"/>
-      <c r="BD8" s="7" t="n"/>
+      <c r="B8" s="368" t="n"/>
+      <c r="C8" s="368" t="n"/>
+      <c r="D8" s="368" t="n"/>
+      <c r="E8" s="368" t="n"/>
+      <c r="F8" s="368" t="n"/>
+      <c r="G8" s="368" t="n"/>
+      <c r="H8" s="368" t="n"/>
+      <c r="I8" s="368" t="n"/>
+      <c r="J8" s="368" t="n"/>
+      <c r="K8" s="368" t="n"/>
+      <c r="L8" s="368" t="n"/>
+      <c r="M8" s="368" t="n"/>
+      <c r="N8" s="368" t="n"/>
+      <c r="O8" s="368" t="n"/>
+      <c r="P8" s="368" t="n"/>
+      <c r="Q8" s="368" t="n"/>
+      <c r="R8" s="368" t="n"/>
+      <c r="S8" s="368" t="n"/>
+      <c r="T8" s="368" t="n"/>
+      <c r="U8" s="368" t="n"/>
+      <c r="V8" s="368" t="n"/>
+      <c r="W8" s="368" t="n"/>
+      <c r="X8" s="368" t="n"/>
+      <c r="Y8" s="368" t="n"/>
+      <c r="Z8" s="368" t="n"/>
+      <c r="AA8" s="368" t="n"/>
+      <c r="AB8" s="368" t="n"/>
+      <c r="AC8" s="368" t="n"/>
+      <c r="AD8" s="368" t="n"/>
+      <c r="AE8" s="368" t="n"/>
+      <c r="AF8" s="368" t="n"/>
+      <c r="AG8" s="368" t="n"/>
+      <c r="AH8" s="368" t="n"/>
+      <c r="AI8" s="368" t="n"/>
+      <c r="AJ8" s="368" t="n"/>
+      <c r="AK8" s="368" t="n"/>
+      <c r="AL8" s="368" t="n"/>
+      <c r="AM8" s="368" t="n"/>
+      <c r="AN8" s="368" t="n"/>
+      <c r="AO8" s="368" t="n"/>
+      <c r="AP8" s="368" t="n"/>
+      <c r="AQ8" s="368" t="n"/>
+      <c r="AR8" s="368" t="n"/>
+      <c r="AS8" s="368" t="n"/>
+      <c r="AT8" s="368" t="n"/>
+      <c r="AU8" s="368" t="n"/>
+      <c r="AV8" s="368" t="n"/>
+      <c r="AW8" s="368" t="n"/>
+      <c r="AX8" s="368" t="n"/>
+      <c r="AY8" s="368" t="n"/>
+      <c r="AZ8" s="368" t="n"/>
+      <c r="BA8" s="368" t="n"/>
+      <c r="BB8" s="368" t="n"/>
+      <c r="BC8" s="368" t="n"/>
+      <c r="BD8" s="369" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="238" t="inlineStr">
@@ -11691,67 +11663,67 @@
       <c r="BC21" s="275" t="n"/>
       <c r="BD21" s="276" t="n"/>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="25" t="inlineStr">
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="267" t="inlineStr">
         <is>
           <t>NOTICE: Controlled lookup lists only. Change values only through formal document control because dropdown behavior and validation depend on this sheet.</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="6" t="n"/>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
-      <c r="I22" s="6" t="n"/>
-      <c r="J22" s="6" t="n"/>
-      <c r="K22" s="6" t="n"/>
-      <c r="L22" s="6" t="n"/>
-      <c r="M22" s="6" t="n"/>
-      <c r="N22" s="6" t="n"/>
-      <c r="O22" s="6" t="n"/>
-      <c r="P22" s="6" t="n"/>
-      <c r="Q22" s="6" t="n"/>
-      <c r="R22" s="6" t="n"/>
-      <c r="S22" s="6" t="n"/>
-      <c r="T22" s="6" t="n"/>
-      <c r="U22" s="6" t="n"/>
-      <c r="V22" s="6" t="n"/>
-      <c r="W22" s="6" t="n"/>
-      <c r="X22" s="6" t="n"/>
-      <c r="Y22" s="6" t="n"/>
-      <c r="Z22" s="6" t="n"/>
-      <c r="AA22" s="6" t="n"/>
-      <c r="AB22" s="6" t="n"/>
-      <c r="AC22" s="6" t="n"/>
-      <c r="AD22" s="6" t="n"/>
-      <c r="AE22" s="6" t="n"/>
-      <c r="AF22" s="6" t="n"/>
-      <c r="AG22" s="6" t="n"/>
-      <c r="AH22" s="6" t="n"/>
-      <c r="AI22" s="6" t="n"/>
-      <c r="AJ22" s="6" t="n"/>
-      <c r="AK22" s="6" t="n"/>
-      <c r="AL22" s="6" t="n"/>
-      <c r="AM22" s="6" t="n"/>
-      <c r="AN22" s="6" t="n"/>
-      <c r="AO22" s="6" t="n"/>
-      <c r="AP22" s="6" t="n"/>
-      <c r="AQ22" s="6" t="n"/>
-      <c r="AR22" s="6" t="n"/>
-      <c r="AS22" s="6" t="n"/>
-      <c r="AT22" s="6" t="n"/>
-      <c r="AU22" s="6" t="n"/>
-      <c r="AV22" s="6" t="n"/>
-      <c r="AW22" s="6" t="n"/>
-      <c r="AX22" s="6" t="n"/>
-      <c r="AY22" s="6" t="n"/>
-      <c r="AZ22" s="6" t="n"/>
-      <c r="BA22" s="6" t="n"/>
-      <c r="BB22" s="6" t="n"/>
-      <c r="BC22" s="6" t="n"/>
-      <c r="BD22" s="7" t="n"/>
+      <c r="B22" s="368" t="n"/>
+      <c r="C22" s="368" t="n"/>
+      <c r="D22" s="368" t="n"/>
+      <c r="E22" s="368" t="n"/>
+      <c r="F22" s="368" t="n"/>
+      <c r="G22" s="368" t="n"/>
+      <c r="H22" s="368" t="n"/>
+      <c r="I22" s="368" t="n"/>
+      <c r="J22" s="368" t="n"/>
+      <c r="K22" s="368" t="n"/>
+      <c r="L22" s="368" t="n"/>
+      <c r="M22" s="368" t="n"/>
+      <c r="N22" s="368" t="n"/>
+      <c r="O22" s="368" t="n"/>
+      <c r="P22" s="368" t="n"/>
+      <c r="Q22" s="368" t="n"/>
+      <c r="R22" s="368" t="n"/>
+      <c r="S22" s="368" t="n"/>
+      <c r="T22" s="368" t="n"/>
+      <c r="U22" s="368" t="n"/>
+      <c r="V22" s="368" t="n"/>
+      <c r="W22" s="368" t="n"/>
+      <c r="X22" s="368" t="n"/>
+      <c r="Y22" s="368" t="n"/>
+      <c r="Z22" s="368" t="n"/>
+      <c r="AA22" s="368" t="n"/>
+      <c r="AB22" s="368" t="n"/>
+      <c r="AC22" s="368" t="n"/>
+      <c r="AD22" s="368" t="n"/>
+      <c r="AE22" s="368" t="n"/>
+      <c r="AF22" s="368" t="n"/>
+      <c r="AG22" s="368" t="n"/>
+      <c r="AH22" s="368" t="n"/>
+      <c r="AI22" s="368" t="n"/>
+      <c r="AJ22" s="368" t="n"/>
+      <c r="AK22" s="368" t="n"/>
+      <c r="AL22" s="368" t="n"/>
+      <c r="AM22" s="368" t="n"/>
+      <c r="AN22" s="368" t="n"/>
+      <c r="AO22" s="368" t="n"/>
+      <c r="AP22" s="368" t="n"/>
+      <c r="AQ22" s="368" t="n"/>
+      <c r="AR22" s="368" t="n"/>
+      <c r="AS22" s="368" t="n"/>
+      <c r="AT22" s="368" t="n"/>
+      <c r="AU22" s="368" t="n"/>
+      <c r="AV22" s="368" t="n"/>
+      <c r="AW22" s="368" t="n"/>
+      <c r="AX22" s="368" t="n"/>
+      <c r="AY22" s="368" t="n"/>
+      <c r="AZ22" s="368" t="n"/>
+      <c r="BA22" s="368" t="n"/>
+      <c r="BB22" s="368" t="n"/>
+      <c r="BC22" s="368" t="n"/>
+      <c r="BD22" s="369" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="18">

--- a/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
@@ -826,6 +826,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -3592,7 +3595,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="246">
     <mergeCell ref="AN13:AU13"/>
     <mergeCell ref="A15:B15"/>
@@ -5435,7 +5437,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="60">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="A22:BD22"/>
@@ -6951,7 +6952,6 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="88">
     <mergeCell ref="N19:W19"/>
     <mergeCell ref="AW2:BD2"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM806_CertLog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM806_ExpiryQ" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM806_ExpiryQ" sheetId="2" state="veryHidden" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM806_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
   </sheets>

--- a/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
@@ -1357,7 +1357,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -1427,7 +1427,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -4195,7 +4195,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -4265,7 +4265,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -5751,7 +5751,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -5821,7 +5821,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -7294,7 +7294,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR + Department Manager</t>
+          <t>HR</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -7364,7 +7364,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>Per authority matrix</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>

--- a/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
@@ -8,9 +8,11 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM806_CertLog" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM806_ExpiryQ" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM806_ExpiryQ" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRM806_Evidence" sheetId="3" state="veryHidden" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="zLISTS" sheetId="4" state="veryHidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_LISTS" sheetId="5" state="hidden" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'FRM806_CertLog'!$1:$13</definedName>
@@ -812,7 +814,7 @@
       <row>0</row>
       <rowOff>257175</rowOff>
     </from>
-    <ext cx="1552575" cy="438150"/>
+    <ext cx="5238750" cy="1514475"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1271,7 +1273,7 @@
       <c r="AV2" s="37" t="n"/>
       <c r="AW2" s="38" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AX2" s="36" t="n"/>
@@ -1327,7 +1329,7 @@
       <c r="AV3" s="37" t="n"/>
       <c r="AW3" s="38" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AX3" s="36" t="n"/>
@@ -1357,7 +1359,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -1427,7 +1429,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -1638,7 +1640,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>Review Period</t>
+          <t>Linked FRM-805</t>
         </is>
       </c>
       <c r="B10" s="6" t="n"/>
@@ -1670,7 +1672,7 @@
       <c r="AB10" s="27" t="n"/>
       <c r="AC10" s="19" t="inlineStr">
         <is>
-          <t>Prepared Date</t>
+          <t>Ref: SOP-801</t>
         </is>
       </c>
       <c r="AD10" s="6" t="n"/>
@@ -1682,7 +1684,11 @@
       <c r="AJ10" s="6" t="n"/>
       <c r="AK10" s="6" t="n"/>
       <c r="AL10" s="7" t="n"/>
-      <c r="AM10" s="22" t="n"/>
+      <c r="AM10" s="22" t="inlineStr">
+        <is>
+          <t>Retain: 5 years per QMS schedule</t>
+        </is>
+      </c>
       <c r="AN10" s="26" t="n"/>
       <c r="AO10" s="26" t="n"/>
       <c r="AP10" s="26" t="n"/>
@@ -3595,6 +3601,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="246">
     <mergeCell ref="AN13:AU13"/>
     <mergeCell ref="A15:B15"/>
@@ -4195,7 +4202,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -4265,7 +4272,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -5437,6 +5444,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="60">
     <mergeCell ref="L4:AP4"/>
     <mergeCell ref="A22:BD22"/>
@@ -5751,7 +5759,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -5821,7 +5829,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -6952,6 +6960,7 @@
     <row r="198" ht="20" customHeight="1"/>
     <row r="199" ht="20" customHeight="1"/>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="0" insertColumns="0" pivotTables="1" deleteRows="0" formatCells="0" formatRows="0" sort="1"/>
   <mergeCells count="88">
     <mergeCell ref="N19:W19"/>
     <mergeCell ref="AW2:BD2"/>
@@ -7294,7 +7303,7 @@
       <c r="AV4" s="37" t="n"/>
       <c r="AW4" s="38" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>HR + Department Manager</t>
         </is>
       </c>
       <c r="AX4" s="36" t="n"/>
@@ -7364,7 +7373,7 @@
       <c r="AV5" s="44" t="n"/>
       <c r="AW5" s="45" t="inlineStr">
         <is>
-          <t>General Manager</t>
+          <t>Per authority matrix</t>
         </is>
       </c>
       <c r="AX5" s="13" t="n"/>
@@ -8668,4 +8677,97 @@
   </headerFooter>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Cross-ref: FRM-805; Parent ref: SOP-801</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
+++ b/04-Bieu-Mau/08-FRM-800/FRM-806_Certification_Tracking_Log.xlsx
@@ -757,7 +757,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="245">
+  <borders count="246">
     <border>
       <left/>
       <right/>
@@ -3511,12 +3511,16 @@
         <color rgb="000078D4"/>
       </bottom>
       <diagonal/>
+    </border>
+    <border>
+      <right/>
+      <bottom/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="494">
+  <cellXfs count="495">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -4707,6 +4711,7 @@
     <xf numFmtId="0" fontId="82" fillId="48" borderId="213" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="47" borderId="245" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4783,6 +4788,50 @@
 </styleSheet>
 </file>
 
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="E9" authorId="0" shapeId="0">
+      <text>
+        <t>Nhân viên
+Tên nhân viên.</t>
+      </text>
+    </comment>
+    <comment ref="Q9" authorId="0" shapeId="0">
+      <text>
+        <t>Chứng nhận
+Tên chứng chỉ.
+Ví dụ: CNC Level 3, Crane operator, First aid.</t>
+      </text>
+    </comment>
+    <comment ref="AC9" authorId="0" shapeId="0">
+      <text>
+        <t xml:space="preserve">Ngày cấp
+</t>
+      </text>
+    </comment>
+    <comment ref="AK9" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày hết hạn
+Theo dõi sát để gia hạn kịp thời.</t>
+      </text>
+    </comment>
+    <comment ref="AS9" authorId="0" shapeId="0">
+      <text>
+        <t>Trạng thái / Hành động
+CURRENT = còn hiệu lực.
+EXPIRING = sắp hết hạn (30 ngày).
+EXPIRED = đã hết hạn → không được thực hiện công việc yêu cầu cert này.
+RENEWING = đang gia hạn.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -4806,6 +4855,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -5417,7 +5469,7 @@
       <c r="BD6" s="30" t="n"/>
     </row>
     <row r="7" ht="4" customHeight="1" s="264">
-      <c r="A7" s="469" t="n"/>
+      <c r="A7" s="494" t="n"/>
       <c r="B7" s="26" t="n"/>
       <c r="C7" s="26" t="n"/>
       <c r="D7" s="26" t="n"/>
@@ -6819,7 +6871,7 @@
       <c r="BD29" s="492" t="n"/>
     </row>
     <row r="30" ht="4" customHeight="1" s="264">
-      <c r="A30" s="469" t="n"/>
+      <c r="A30" s="494" t="n"/>
       <c r="B30" s="26" t="n"/>
       <c r="C30" s="26" t="n"/>
       <c r="D30" s="26" t="n"/>
@@ -6879,7 +6931,7 @@
     <row r="31" ht="24" customHeight="1" s="264">
       <c r="A31" s="493" t="inlineStr">
         <is>
-          <t>NOTICE — Track expiring certifications. Ref: SOP-801. Retain: 5 years.</t>
+          <t>NOTICE — Track all expiring certifications. Alert 60 days before expiry. Ref: SOP-801. Retain: 5 years.</t>
         </is>
       </c>
       <c r="B31" s="471" t="n"/>
@@ -7088,6 +7140,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
